--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -579,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV1 — 03/07/2026  |  Elaborado por: Ilson dos Santos Azevedo — Supervisor de Planejamento</t>
+          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV1 — 03/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
         </is>
       </c>
     </row>
@@ -7869,12 +7869,12 @@
     <mergeCell ref="B63:B66"/>
     <mergeCell ref="E23:E31"/>
     <mergeCell ref="D111:D117"/>
+    <mergeCell ref="E143:E149"/>
     <mergeCell ref="D63:D66"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="D10:D13"/>
+    <mergeCell ref="C189:C194"/>
     <mergeCell ref="C143:C149"/>
-    <mergeCell ref="E143:E149"/>
-    <mergeCell ref="C189:C194"/>
     <mergeCell ref="E189:E194"/>
     <mergeCell ref="B14:B22"/>
     <mergeCell ref="A36:A39"/>
@@ -7926,7 +7926,6 @@
     <mergeCell ref="E180:E182"/>
     <mergeCell ref="B93:B99"/>
     <mergeCell ref="M63:M66"/>
-    <mergeCell ref="C205:C206"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A207:A208"/>
     <mergeCell ref="A67:A70"/>
@@ -7992,6 +7991,7 @@
     <mergeCell ref="A209:A211"/>
     <mergeCell ref="C209:C211"/>
     <mergeCell ref="B82:B92"/>
+    <mergeCell ref="C205:C206"/>
     <mergeCell ref="D143:D149"/>
     <mergeCell ref="C63:C66"/>
     <mergeCell ref="M67:M70"/>

--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Push List REV1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Push List REV2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M211"/>
+  <dimension ref="A1:M217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -579,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV1 — 03/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
+          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV2 — 03/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
         </is>
       </c>
     </row>
@@ -7724,10 +7724,8 @@
           <t>Platô Central</t>
         </is>
       </c>
-      <c r="E209" s="9" t="inlineStr">
-        <is>
-          <t>S/F</t>
-        </is>
+      <c r="E209" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="F209" s="9" t="n">
         <v>1</v>
@@ -7820,8 +7818,234 @@
       <c r="L211" s="9" t="inlineStr"/>
       <c r="M211" s="12" t="n"/>
     </row>
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
+          <t>Platô Central</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D212" s="5" t="inlineStr">
+        <is>
+          <t>Platô Central</t>
+        </is>
+      </c>
+      <c r="E212" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G212" s="6" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H212" s="7" t="inlineStr">
+        <is>
+          <t>Remoção de Canaletas</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" s="4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K212" s="4" t="inlineStr"/>
+      <c r="L212" s="4" t="inlineStr"/>
+      <c r="M212" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="16" customHeight="1">
+      <c r="A213" s="8" t="n"/>
+      <c r="B213" s="8" t="n"/>
+      <c r="C213" s="8" t="n"/>
+      <c r="D213" s="8" t="n"/>
+      <c r="E213" s="8" t="n"/>
+      <c r="F213" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G213" s="10" t="inlineStr">
+        <is>
+          <t>Terraplanagem</t>
+        </is>
+      </c>
+      <c r="H213" s="11" t="inlineStr">
+        <is>
+          <t>Regularização e adensamento do Platôr Central</t>
+        </is>
+      </c>
+      <c r="I213" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" s="9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K213" s="9" t="inlineStr"/>
+      <c r="L213" s="9" t="inlineStr"/>
+      <c r="M213" s="8" t="n"/>
+    </row>
+    <row r="214" ht="16" customHeight="1">
+      <c r="A214" s="12" t="n"/>
+      <c r="B214" s="12" t="n"/>
+      <c r="C214" s="12" t="n"/>
+      <c r="D214" s="12" t="n"/>
+      <c r="E214" s="12" t="n"/>
+      <c r="F214" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G214" s="6" t="inlineStr">
+        <is>
+          <t>Geral / 5S</t>
+        </is>
+      </c>
+      <c r="H214" s="7" t="inlineStr">
+        <is>
+          <t>Limpeza geral e reorganização da área</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J214" s="4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K214" s="4" t="inlineStr"/>
+      <c r="L214" s="4" t="inlineStr"/>
+      <c r="M214" s="12" t="n"/>
+    </row>
+    <row r="215" ht="16" customHeight="1">
+      <c r="A215" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="B215" s="13" t="inlineStr">
+        <is>
+          <t>Platô Central</t>
+        </is>
+      </c>
+      <c r="C215" s="9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D215" s="13" t="inlineStr">
+        <is>
+          <t>Platô Central</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F215" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="10" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H215" s="11" t="inlineStr">
+        <is>
+          <t>Remoção de Canaletas</t>
+        </is>
+      </c>
+      <c r="I215" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" s="9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K215" s="9" t="inlineStr"/>
+      <c r="L215" s="9" t="inlineStr"/>
+      <c r="M215" s="9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="16" customHeight="1">
+      <c r="A216" s="8" t="n"/>
+      <c r="B216" s="8" t="n"/>
+      <c r="C216" s="8" t="n"/>
+      <c r="D216" s="8" t="n"/>
+      <c r="E216" s="8" t="n"/>
+      <c r="F216" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G216" s="6" t="inlineStr">
+        <is>
+          <t>Terraplanagem</t>
+        </is>
+      </c>
+      <c r="H216" s="7" t="inlineStr">
+        <is>
+          <t>Regularização e adensamento do Platôr Central</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" s="4" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr"/>
+      <c r="L216" s="4" t="inlineStr"/>
+      <c r="M216" s="8" t="n"/>
+    </row>
+    <row r="217" ht="16" customHeight="1">
+      <c r="A217" s="12" t="n"/>
+      <c r="B217" s="12" t="n"/>
+      <c r="C217" s="12" t="n"/>
+      <c r="D217" s="12" t="n"/>
+      <c r="E217" s="12" t="n"/>
+      <c r="F217" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G217" s="10" t="inlineStr">
+        <is>
+          <t>Geral / 5S</t>
+        </is>
+      </c>
+      <c r="H217" s="11" t="inlineStr">
+        <is>
+          <t>Limpeza geral e reorganização da área</t>
+        </is>
+      </c>
+      <c r="I217" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" s="9" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K217" s="9" t="inlineStr"/>
+      <c r="L217" s="9" t="inlineStr"/>
+      <c r="M217" s="12" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="218">
+  <mergeCells count="230">
     <mergeCell ref="E203:E204"/>
     <mergeCell ref="B50:B55"/>
     <mergeCell ref="E118:E124"/>
@@ -7829,6 +8053,7 @@
     <mergeCell ref="D180:D182"/>
     <mergeCell ref="E183:E188"/>
     <mergeCell ref="A136:A142"/>
+    <mergeCell ref="D212:D214"/>
     <mergeCell ref="M50:M55"/>
     <mergeCell ref="D46:D49"/>
     <mergeCell ref="M203:M204"/>
@@ -7846,6 +8071,7 @@
     <mergeCell ref="M14:M22"/>
     <mergeCell ref="A125:A135"/>
     <mergeCell ref="E207:E208"/>
+    <mergeCell ref="B215:B217"/>
     <mergeCell ref="M36:M39"/>
     <mergeCell ref="B205:B206"/>
     <mergeCell ref="A203:A204"/>
@@ -7853,10 +8079,14 @@
     <mergeCell ref="D157:D167"/>
     <mergeCell ref="E125:E135"/>
     <mergeCell ref="A195:A200"/>
+    <mergeCell ref="A212:A214"/>
     <mergeCell ref="D168:D173"/>
+    <mergeCell ref="C212:C214"/>
     <mergeCell ref="A63:A66"/>
     <mergeCell ref="E100:E110"/>
     <mergeCell ref="A10:A13"/>
+    <mergeCell ref="C215:C217"/>
+    <mergeCell ref="E215:E217"/>
     <mergeCell ref="M71:M81"/>
     <mergeCell ref="A174:A176"/>
     <mergeCell ref="B100:B110"/>
@@ -7869,12 +8099,12 @@
     <mergeCell ref="B63:B66"/>
     <mergeCell ref="E23:E31"/>
     <mergeCell ref="D111:D117"/>
-    <mergeCell ref="E143:E149"/>
     <mergeCell ref="D63:D66"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="D10:D13"/>
+    <mergeCell ref="C143:C149"/>
+    <mergeCell ref="E143:E149"/>
     <mergeCell ref="C189:C194"/>
-    <mergeCell ref="C143:C149"/>
     <mergeCell ref="E189:E194"/>
     <mergeCell ref="B14:B22"/>
     <mergeCell ref="A36:A39"/>
@@ -7924,8 +8154,10 @@
     <mergeCell ref="C180:C182"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="E180:E182"/>
+    <mergeCell ref="M212:M214"/>
     <mergeCell ref="B93:B99"/>
     <mergeCell ref="M63:M66"/>
+    <mergeCell ref="C205:C206"/>
     <mergeCell ref="B32:B35"/>
     <mergeCell ref="A207:A208"/>
     <mergeCell ref="A67:A70"/>
@@ -7941,13 +8173,16 @@
     <mergeCell ref="B46:B49"/>
     <mergeCell ref="E67:E70"/>
     <mergeCell ref="D150:D156"/>
+    <mergeCell ref="A215:A217"/>
     <mergeCell ref="B143:B149"/>
     <mergeCell ref="D183:D188"/>
     <mergeCell ref="A205:A206"/>
+    <mergeCell ref="M215:M217"/>
     <mergeCell ref="D125:D135"/>
     <mergeCell ref="A23:A31"/>
     <mergeCell ref="A143:A149"/>
     <mergeCell ref="C183:C188"/>
+    <mergeCell ref="B212:B214"/>
     <mergeCell ref="M46:M49"/>
     <mergeCell ref="M177:M179"/>
     <mergeCell ref="B10:B13"/>
@@ -7982,6 +8217,7 @@
     <mergeCell ref="B189:B194"/>
     <mergeCell ref="B71:B81"/>
     <mergeCell ref="M4:M9"/>
+    <mergeCell ref="D215:D217"/>
     <mergeCell ref="C43:C45"/>
     <mergeCell ref="A56:A62"/>
     <mergeCell ref="C56:C62"/>
@@ -7991,7 +8227,7 @@
     <mergeCell ref="A209:A211"/>
     <mergeCell ref="C209:C211"/>
     <mergeCell ref="B82:B92"/>
-    <mergeCell ref="C205:C206"/>
+    <mergeCell ref="E212:E214"/>
     <mergeCell ref="D143:D149"/>
     <mergeCell ref="C63:C66"/>
     <mergeCell ref="M67:M70"/>

--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Push List REV2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Push List REV3" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -556,17 +556,17 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -579,7 +579,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV2 — 03/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
+          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV3 — 03/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Local Nº</t>
+          <t>Local</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Nome do Local</t>
+          <t>Nome</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t># Ativ.</t>
+          <t>#Atv</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Atividade / Descrição</t>
+          <t>Atividade</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Avanço (%)</t>
+          <t>Avanço(%)</t>
         </is>
       </c>
     </row>

--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -556,17 +556,17 @@
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,12 +596,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>Local Nº</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Nome</t>
+          <t>Nome do Local</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>#Atv</t>
+          <t># Ativ.</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Atividade</t>
+          <t>Atividade / Descrição</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Avanço(%)</t>
+          <t>Avanço (%)</t>
         </is>
       </c>
     </row>

--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,11 @@
     <font>
       <name val="Calibri"/>
       <color rgb="00C8D8F0"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00B0BEC5"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -149,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -172,6 +177,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -181,6 +189,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -688,56 +699,56 @@
       <c r="I4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr"/>
       <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="8" t="n"/>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="9" t="n">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
         <is>
           <t>Recolocação da canaleta na Berma da escada</t>
         </is>
       </c>
-      <c r="I5" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr"/>
-      <c r="M5" s="8" t="n"/>
+      <c r="I5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr"/>
+      <c r="L5" s="10" t="inlineStr"/>
+      <c r="M5" s="9" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="8" t="n"/>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
       <c r="F6" s="4" t="n">
         <v>3</v>
       </c>
@@ -754,52 +765,52 @@
       <c r="I6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="8" t="n"/>
+      <c r="M6" s="9" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="8" t="n"/>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-      <c r="E7" s="8" t="n"/>
-      <c r="F7" s="9" t="n">
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G7" s="10" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>Recomposição do talude / recompactação do solo próximo à Escada 1</t>
         </is>
       </c>
-      <c r="I7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K7" s="9" t="inlineStr"/>
-      <c r="L7" s="9" t="inlineStr"/>
-      <c r="M7" s="8" t="n"/>
+      <c r="I7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr"/>
+      <c r="L7" s="10" t="inlineStr"/>
+      <c r="M7" s="9" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="8" t="n"/>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n"/>
+      <c r="A8" s="9" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
       <c r="F8" s="4" t="n">
         <v>5</v>
       </c>
@@ -816,45 +827,45 @@
       <c r="I8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="inlineStr"/>
-      <c r="M8" s="8" t="n"/>
+      <c r="M8" s="9" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="9" t="n">
+      <c r="A9" s="14" t="n"/>
+      <c r="B9" s="14" t="n"/>
+      <c r="C9" s="14" t="n"/>
+      <c r="D9" s="14" t="n"/>
+      <c r="E9" s="14" t="n"/>
+      <c r="F9" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G9" s="10" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I9" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr"/>
-      <c r="L9" s="9" t="inlineStr"/>
-      <c r="M9" s="12" t="n"/>
+      <c r="I9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr"/>
+      <c r="L9" s="10" t="inlineStr"/>
+      <c r="M9" s="14" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -894,56 +905,56 @@
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="8" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="9" t="n">
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="G11" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>Corte da crista do talude para padronização da Berma da calha</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K11" s="9" t="inlineStr"/>
-      <c r="L11" s="9" t="inlineStr"/>
-      <c r="M11" s="8" t="n"/>
+      <c r="I11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr"/>
+      <c r="L11" s="10" t="inlineStr"/>
+      <c r="M11" s="9" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="8" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
       <c r="F12" s="4" t="n">
         <v>3</v>
       </c>
@@ -960,45 +971,45 @@
       <c r="I12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
       <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="8" t="n"/>
+      <c r="M12" s="9" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="9" t="n">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K13" s="9" t="inlineStr"/>
-      <c r="L13" s="9" t="inlineStr"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="I13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr"/>
+      <c r="L13" s="10" t="inlineStr"/>
+      <c r="M13" s="14" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="4" t="n">
@@ -1038,56 +1049,56 @@
       <c r="I14" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="8" t="n"/>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
-      <c r="F15" s="9" t="n">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama no talude (trecho com lacunas de solo exposto)</t>
         </is>
       </c>
-      <c r="I15" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr"/>
-      <c r="M15" s="8" t="n"/>
+      <c r="I15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr"/>
+      <c r="M15" s="9" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="8" t="n"/>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
+      <c r="A16" s="9" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
       <c r="F16" s="4" t="n">
         <v>3</v>
       </c>
@@ -1104,52 +1115,52 @@
       <c r="I16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="4" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="8" t="n"/>
+      <c r="M16" s="9" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="8" t="n"/>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="9" t="n">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G17" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr">
+      <c r="G17" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>Acerto do terreno superficial do platô</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K17" s="9" t="inlineStr"/>
-      <c r="L17" s="9" t="inlineStr"/>
-      <c r="M17" s="8" t="n"/>
+      <c r="I17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr"/>
+      <c r="L17" s="10" t="inlineStr"/>
+      <c r="M17" s="9" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="8" t="n"/>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
+      <c r="A18" s="9" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
       <c r="F18" s="4" t="n">
         <v>5</v>
       </c>
@@ -1166,52 +1177,52 @@
       <c r="I18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="4" t="inlineStr">
+      <c r="J18" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="8" t="n"/>
+      <c r="M18" s="9" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="8" t="n"/>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="n">
+      <c r="A19" s="9" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr">
+      <c r="G19" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
         <is>
           <t>Rejuntamento com argamassa mista (traço 1:3) nas canaletas</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="9" t="inlineStr"/>
-      <c r="M19" s="8" t="n"/>
+      <c r="I19" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr"/>
+      <c r="L19" s="10" t="inlineStr"/>
+      <c r="M19" s="9" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="8" t="n"/>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
+      <c r="A20" s="9" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
       <c r="F20" s="4" t="n">
         <v>7</v>
       </c>
@@ -1228,52 +1239,52 @@
       <c r="I20" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr"/>
-      <c r="M20" s="8" t="n"/>
+      <c r="M20" s="9" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="8" t="n"/>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="9" t="n">
+      <c r="A21" s="9" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="G21" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr">
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
         <is>
           <t>Remoção do excedente de terra do platô</t>
         </is>
       </c>
-      <c r="I21" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr"/>
-      <c r="L21" s="9" t="inlineStr"/>
-      <c r="M21" s="8" t="n"/>
+      <c r="I21" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr"/>
+      <c r="L21" s="10" t="inlineStr"/>
+      <c r="M21" s="9" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
+      <c r="A22" s="14" t="n"/>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="14" t="n"/>
       <c r="F22" s="4" t="n">
         <v>9</v>
       </c>
@@ -1290,72 +1301,72 @@
       <c r="I22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="12" t="n"/>
+      <c r="M22" s="14" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Área Perimetral da Escada 2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="15" t="inlineStr">
         <is>
           <t>Área Perimetral da Escada 2</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
+      <c r="E23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr">
         <is>
           <t>Acerto e aterro no platô abaixo da berma (laterais da Escada 2) com compactação</t>
         </is>
       </c>
-      <c r="I23" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K23" s="9" t="inlineStr"/>
-      <c r="L23" s="9" t="inlineStr"/>
-      <c r="M23" s="9" t="inlineStr">
+      <c r="I23" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr"/>
+      <c r="L23" s="10" t="inlineStr"/>
+      <c r="M23" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="8" t="n"/>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
       <c r="F24" s="4" t="n">
         <v>2</v>
       </c>
@@ -1372,52 +1383,52 @@
       <c r="I24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="inlineStr"/>
-      <c r="M24" s="8" t="n"/>
+      <c r="M24" s="9" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="8" t="n"/>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="9" t="n">
+      <c r="A25" s="9" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="inlineStr">
         <is>
           <t>Recomposição do talude / recompactação do solo em relação ao platô</t>
         </is>
       </c>
-      <c r="I25" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K25" s="9" t="inlineStr"/>
-      <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="8" t="n"/>
+      <c r="I25" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr"/>
+      <c r="L25" s="10" t="inlineStr"/>
+      <c r="M25" s="9" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="8" t="n"/>
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
+      <c r="A26" s="9" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
       <c r="F26" s="4" t="n">
         <v>4</v>
       </c>
@@ -1434,52 +1445,52 @@
       <c r="I26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
       <c r="L26" s="4" t="inlineStr"/>
-      <c r="M26" s="8" t="n"/>
+      <c r="M26" s="9" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="8" t="n"/>
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="9" t="n">
+      <c r="A27" s="9" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="10" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama em toda a região perimetral da Escada 2</t>
         </is>
       </c>
-      <c r="I27" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K27" s="9" t="inlineStr"/>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="8" t="n"/>
+      <c r="I27" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr"/>
+      <c r="L27" s="10" t="inlineStr"/>
+      <c r="M27" s="9" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="8" t="n"/>
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
+      <c r="A28" s="9" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
       <c r="F28" s="4" t="n">
         <v>6</v>
       </c>
@@ -1496,52 +1507,52 @@
       <c r="I28" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J28" s="4" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4" t="inlineStr"/>
-      <c r="M28" s="8" t="n"/>
+      <c r="M28" s="9" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="8" t="n"/>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="9" t="n">
+      <c r="A29" s="9" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G29" s="10" t="inlineStr">
+      <c r="G29" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H29" s="11" t="inlineStr">
+      <c r="H29" s="12" t="inlineStr">
         <is>
           <t>Remoção do excedente de terra do platô</t>
         </is>
       </c>
-      <c r="I29" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K29" s="9" t="inlineStr"/>
-      <c r="L29" s="9" t="inlineStr"/>
-      <c r="M29" s="8" t="n"/>
+      <c r="I29" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr"/>
+      <c r="L29" s="10" t="inlineStr"/>
+      <c r="M29" s="9" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="8" t="n"/>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
+      <c r="A30" s="9" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
       <c r="F30" s="4" t="n">
         <v>8</v>
       </c>
@@ -1558,45 +1569,45 @@
       <c r="I30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="4" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="inlineStr"/>
-      <c r="M30" s="8" t="n"/>
+      <c r="M30" s="9" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="9" t="n">
+      <c r="A31" s="14" t="n"/>
+      <c r="B31" s="14" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I31" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K31" s="9" t="inlineStr"/>
-      <c r="L31" s="9" t="inlineStr"/>
-      <c r="M31" s="12" t="n"/>
+      <c r="I31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr"/>
+      <c r="L31" s="10" t="inlineStr"/>
+      <c r="M31" s="14" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="4" t="n">
@@ -1636,56 +1647,56 @@
       <c r="I32" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="inlineStr"/>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="8" t="n"/>
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="9" t="n">
+      <c r="A33" s="9" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="10" t="inlineStr">
+      <c r="G33" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e recompactação do talude</t>
         </is>
       </c>
-      <c r="I33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K33" s="9" t="inlineStr"/>
-      <c r="L33" s="9" t="inlineStr"/>
-      <c r="M33" s="8" t="n"/>
+      <c r="I33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr"/>
+      <c r="L33" s="10" t="inlineStr"/>
+      <c r="M33" s="9" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="8" t="n"/>
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
+      <c r="A34" s="9" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
       <c r="F34" s="4" t="n">
         <v>3</v>
       </c>
@@ -1702,45 +1713,45 @@
       <c r="I34" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="J34" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="4" t="inlineStr"/>
-      <c r="M34" s="8" t="n"/>
+      <c r="M34" s="9" t="n"/>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="9" t="n">
+      <c r="A35" s="14" t="n"/>
+      <c r="B35" s="14" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
+      <c r="F35" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G35" s="10" t="inlineStr">
+      <c r="G35" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K35" s="9" t="inlineStr"/>
-      <c r="L35" s="9" t="inlineStr"/>
-      <c r="M35" s="12" t="n"/>
+      <c r="I35" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr"/>
+      <c r="L35" s="10" t="inlineStr"/>
+      <c r="M35" s="14" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="4" t="n">
@@ -1780,56 +1791,56 @@
       <c r="I36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="inlineStr"/>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="M36" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="8" t="n"/>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="9" t="n">
+      <c r="A37" s="9" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e recompactação do talude</t>
         </is>
       </c>
-      <c r="I37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K37" s="9" t="inlineStr"/>
-      <c r="L37" s="9" t="inlineStr"/>
-      <c r="M37" s="8" t="n"/>
+      <c r="I37" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr"/>
+      <c r="L37" s="10" t="inlineStr"/>
+      <c r="M37" s="9" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="8" t="n"/>
-      <c r="B38" s="8" t="n"/>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
+      <c r="A38" s="9" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
       <c r="F38" s="4" t="n">
         <v>3</v>
       </c>
@@ -1846,45 +1857,45 @@
       <c r="I38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="inlineStr"/>
-      <c r="M38" s="8" t="n"/>
+      <c r="M38" s="9" t="n"/>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="9" t="n">
+      <c r="A39" s="14" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G39" s="10" t="inlineStr">
+      <c r="G39" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H39" s="11" t="inlineStr">
+      <c r="H39" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K39" s="9" t="inlineStr"/>
-      <c r="L39" s="9" t="inlineStr"/>
-      <c r="M39" s="12" t="n"/>
+      <c r="I39" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr"/>
+      <c r="L39" s="10" t="inlineStr"/>
+      <c r="M39" s="14" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="4" t="n">
@@ -1924,56 +1935,56 @@
       <c r="I40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="4" t="inlineStr">
+      <c r="J40" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="inlineStr"/>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="M40" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="8" t="n"/>
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="9" t="n">
+      <c r="A41" s="9" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G41" s="10" t="inlineStr">
+      <c r="G41" s="11" t="inlineStr">
         <is>
           <t>Macrodrenagem / 5S</t>
         </is>
       </c>
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="12" t="inlineStr">
         <is>
           <t>Remoção das sobras de canaleta e demais materiais residuais</t>
         </is>
       </c>
-      <c r="I41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K41" s="9" t="inlineStr"/>
-      <c r="L41" s="9" t="inlineStr"/>
-      <c r="M41" s="8" t="n"/>
+      <c r="I41" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr"/>
+      <c r="L41" s="10" t="inlineStr"/>
+      <c r="M41" s="9" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
+      <c r="A42" s="14" t="n"/>
+      <c r="B42" s="14" t="n"/>
+      <c r="C42" s="14" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
       <c r="F42" s="4" t="n">
         <v>3</v>
       </c>
@@ -1990,72 +2001,72 @@
       <c r="I42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr"/>
       <c r="L42" s="4" t="inlineStr"/>
-      <c r="M42" s="12" t="n"/>
+      <c r="M42" s="14" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B43" s="13" t="inlineStr">
+      <c r="B43" s="15" t="inlineStr">
         <is>
           <t>Superfície da Berma — Cota 691</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="D43" s="13" t="inlineStr">
+      <c r="D43" s="15" t="inlineStr">
         <is>
           <t>Superfície da Berma — Cota 691</t>
         </is>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="10" t="inlineStr">
+      <c r="F43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
         <is>
           <t>Macrodrenagem / 5S</t>
         </is>
       </c>
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="12" t="inlineStr">
         <is>
           <t>Remoção de todo o solo excedente das atividades de macrodrenagem da Berma</t>
         </is>
       </c>
-      <c r="I43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K43" s="9" t="inlineStr"/>
-      <c r="L43" s="9" t="inlineStr"/>
-      <c r="M43" s="9" t="inlineStr">
+      <c r="I43" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr"/>
+      <c r="L43" s="10" t="inlineStr"/>
+      <c r="M43" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="8" t="n"/>
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
+      <c r="A44" s="9" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
       <c r="F44" s="4" t="n">
         <v>2</v>
       </c>
@@ -2072,45 +2083,45 @@
       <c r="I44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="4" t="inlineStr">
+      <c r="J44" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr"/>
       <c r="L44" s="4" t="inlineStr"/>
-      <c r="M44" s="8" t="n"/>
+      <c r="M44" s="9" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="12" t="n"/>
-      <c r="B45" s="12" t="n"/>
-      <c r="C45" s="12" t="n"/>
-      <c r="D45" s="12" t="n"/>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="9" t="n">
+      <c r="A45" s="14" t="n"/>
+      <c r="B45" s="14" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
+      <c r="F45" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="10" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="12" t="inlineStr">
         <is>
           <t>Organização e limpeza geral da área da Berma (cota 691)</t>
         </is>
       </c>
-      <c r="I45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K45" s="9" t="inlineStr"/>
-      <c r="L45" s="9" t="inlineStr"/>
-      <c r="M45" s="12" t="n"/>
+      <c r="I45" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr"/>
+      <c r="L45" s="10" t="inlineStr"/>
+      <c r="M45" s="14" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="4" t="n">
@@ -2150,56 +2161,56 @@
       <c r="I46" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="inlineStr"/>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="8" t="n"/>
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="9" t="n">
+      <c r="A47" s="9" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G47" s="10" t="inlineStr">
+      <c r="G47" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H47" s="11" t="inlineStr">
+      <c r="H47" s="12" t="inlineStr">
         <is>
           <t>Remoção do entulho das canaletas</t>
         </is>
       </c>
-      <c r="I47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K47" s="9" t="inlineStr"/>
-      <c r="L47" s="9" t="inlineStr"/>
-      <c r="M47" s="8" t="n"/>
+      <c r="I47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="inlineStr"/>
+      <c r="L47" s="10" t="inlineStr"/>
+      <c r="M47" s="9" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="8" t="n"/>
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
       <c r="F48" s="4" t="n">
         <v>3</v>
       </c>
@@ -2216,45 +2227,45 @@
       <c r="I48" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr"/>
       <c r="L48" s="4" t="inlineStr"/>
-      <c r="M48" s="8" t="n"/>
+      <c r="M48" s="9" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="12" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="9" t="n">
+      <c r="A49" s="14" t="n"/>
+      <c r="B49" s="14" t="n"/>
+      <c r="C49" s="14" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
+      <c r="F49" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G49" s="10" t="inlineStr">
+      <c r="G49" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H49" s="11" t="inlineStr">
+      <c r="H49" s="12" t="inlineStr">
         <is>
           <t>Remoção de grama excedente e limpeza geral da área</t>
         </is>
       </c>
-      <c r="I49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K49" s="9" t="inlineStr"/>
-      <c r="L49" s="9" t="inlineStr"/>
-      <c r="M49" s="12" t="n"/>
+      <c r="I49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr"/>
+      <c r="L49" s="10" t="inlineStr"/>
+      <c r="M49" s="14" t="n"/>
     </row>
     <row r="50" ht="16" customHeight="1">
       <c r="A50" s="4" t="n">
@@ -2294,56 +2305,56 @@
       <c r="I50" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="4" t="inlineStr">
+      <c r="J50" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr"/>
       <c r="L50" s="4" t="inlineStr"/>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="M50" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="8" t="n"/>
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="9" t="n">
+      <c r="A51" s="9" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G51" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H51" s="11" t="inlineStr">
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H51" s="12" t="inlineStr">
         <is>
           <t>Reaterro com compactação das faces laterais da Escada 3</t>
         </is>
       </c>
-      <c r="I51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K51" s="9" t="inlineStr"/>
-      <c r="L51" s="9" t="inlineStr"/>
-      <c r="M51" s="8" t="n"/>
+      <c r="I51" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr"/>
+      <c r="L51" s="10" t="inlineStr"/>
+      <c r="M51" s="9" t="n"/>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="8" t="n"/>
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
+      <c r="A52" s="9" t="n"/>
+      <c r="B52" s="9" t="n"/>
+      <c r="C52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
       <c r="F52" s="4" t="n">
         <v>3</v>
       </c>
@@ -2360,52 +2371,52 @@
       <c r="I52" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J52" s="4" t="inlineStr">
+      <c r="J52" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="4" t="inlineStr"/>
-      <c r="M52" s="8" t="n"/>
+      <c r="M52" s="9" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="8" t="n"/>
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="9" t="n">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="9" t="n"/>
+      <c r="C53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G53" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H53" s="11" t="inlineStr">
+      <c r="G53" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H53" s="12" t="inlineStr">
         <is>
           <t>Aplicação de argamassa superficial de regularização da Escada 3</t>
         </is>
       </c>
-      <c r="I53" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K53" s="9" t="inlineStr"/>
-      <c r="L53" s="9" t="inlineStr"/>
-      <c r="M53" s="8" t="n"/>
+      <c r="I53" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr"/>
+      <c r="L53" s="10" t="inlineStr"/>
+      <c r="M53" s="9" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="8" t="n"/>
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
+      <c r="A54" s="9" t="n"/>
+      <c r="B54" s="9" t="n"/>
+      <c r="C54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
       <c r="F54" s="4" t="n">
         <v>5</v>
       </c>
@@ -2422,45 +2433,45 @@
       <c r="I54" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J54" s="4" t="inlineStr">
+      <c r="J54" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr"/>
       <c r="L54" s="4" t="inlineStr"/>
-      <c r="M54" s="8" t="n"/>
+      <c r="M54" s="9" t="n"/>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="12" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="9" t="n">
+      <c r="A55" s="14" t="n"/>
+      <c r="B55" s="14" t="n"/>
+      <c r="C55" s="14" t="n"/>
+      <c r="D55" s="14" t="n"/>
+      <c r="E55" s="14" t="n"/>
+      <c r="F55" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G55" s="10" t="inlineStr">
+      <c r="G55" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H55" s="11" t="inlineStr">
+      <c r="H55" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e remoção de entulho e resíduos de concretagem</t>
         </is>
       </c>
-      <c r="I55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K55" s="9" t="inlineStr"/>
-      <c r="L55" s="9" t="inlineStr"/>
-      <c r="M55" s="12" t="n"/>
+      <c r="I55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr"/>
+      <c r="L55" s="10" t="inlineStr"/>
+      <c r="M55" s="14" t="n"/>
     </row>
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="n">
@@ -2500,56 +2511,56 @@
       <c r="I56" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
+      <c r="J56" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr"/>
       <c r="L56" s="4" t="inlineStr"/>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="M56" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="8" t="n"/>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="9" t="n">
+      <c r="A57" s="9" t="n"/>
+      <c r="B57" s="9" t="n"/>
+      <c r="C57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G57" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H57" s="11" t="inlineStr">
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H57" s="12" t="inlineStr">
         <is>
           <t>Nivelamento superficial da base da vala da berma</t>
         </is>
       </c>
-      <c r="I57" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K57" s="9" t="inlineStr"/>
-      <c r="L57" s="9" t="inlineStr"/>
-      <c r="M57" s="8" t="n"/>
+      <c r="I57" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr"/>
+      <c r="L57" s="10" t="inlineStr"/>
+      <c r="M57" s="9" t="n"/>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="8" t="n"/>
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
+      <c r="A58" s="9" t="n"/>
+      <c r="B58" s="9" t="n"/>
+      <c r="C58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
       <c r="F58" s="4" t="n">
         <v>3</v>
       </c>
@@ -2566,52 +2577,52 @@
       <c r="I58" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr"/>
       <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="8" t="n"/>
+      <c r="M58" s="9" t="n"/>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="8" t="n"/>
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="9" t="n">
+      <c r="A59" s="9" t="n"/>
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G59" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H59" s="11" t="inlineStr">
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H59" s="12" t="inlineStr">
         <is>
           <t>Reinstalação das canaletas da berma com nivelamento correto</t>
         </is>
       </c>
-      <c r="I59" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K59" s="9" t="inlineStr"/>
-      <c r="L59" s="9" t="inlineStr"/>
-      <c r="M59" s="8" t="n"/>
+      <c r="I59" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr"/>
+      <c r="L59" s="10" t="inlineStr"/>
+      <c r="M59" s="9" t="n"/>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="8" t="n"/>
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
+      <c r="A60" s="9" t="n"/>
+      <c r="B60" s="9" t="n"/>
+      <c r="C60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
       <c r="F60" s="4" t="n">
         <v>5</v>
       </c>
@@ -2628,52 +2639,52 @@
       <c r="I60" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J60" s="4" t="inlineStr">
+      <c r="J60" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr"/>
       <c r="L60" s="4" t="inlineStr"/>
-      <c r="M60" s="8" t="n"/>
+      <c r="M60" s="9" t="n"/>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="8" t="n"/>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="9" t="n">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="9" t="n"/>
+      <c r="C61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H61" s="11" t="inlineStr">
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H61" s="12" t="inlineStr">
         <is>
           <t>Aplicação de argamassa de regularização (traço 1:3) nas canaletas</t>
         </is>
       </c>
-      <c r="I61" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K61" s="9" t="inlineStr"/>
-      <c r="L61" s="9" t="inlineStr"/>
-      <c r="M61" s="8" t="n"/>
+      <c r="I61" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="inlineStr"/>
+      <c r="L61" s="10" t="inlineStr"/>
+      <c r="M61" s="9" t="n"/>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="12" t="n"/>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
+      <c r="A62" s="14" t="n"/>
+      <c r="B62" s="14" t="n"/>
+      <c r="C62" s="14" t="n"/>
+      <c r="D62" s="14" t="n"/>
+      <c r="E62" s="14" t="n"/>
       <c r="F62" s="4" t="n">
         <v>7</v>
       </c>
@@ -2690,72 +2701,72 @@
       <c r="I62" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr"/>
       <c r="L62" s="4" t="inlineStr"/>
-      <c r="M62" s="12" t="n"/>
+      <c r="M62" s="14" t="n"/>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="9" t="n">
+      <c r="A63" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B63" s="13" t="inlineStr">
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>Talude da Bacia — Curva (Escada 3)</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D63" s="15" t="inlineStr">
         <is>
           <t>Talude da Bacia — Curva (Escada 3)</t>
         </is>
       </c>
-      <c r="E63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" s="10" t="inlineStr">
+      <c r="E63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H63" s="11" t="inlineStr">
+      <c r="H63" s="12" t="inlineStr">
         <is>
           <t>Remoção das gramas mal instaladas e deslocadas do talude</t>
         </is>
       </c>
-      <c r="I63" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K63" s="9" t="inlineStr"/>
-      <c r="L63" s="9" t="inlineStr"/>
-      <c r="M63" s="9" t="inlineStr">
+      <c r="I63" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr"/>
+      <c r="L63" s="10" t="inlineStr"/>
+      <c r="M63" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="8" t="n"/>
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="9" t="n"/>
+      <c r="C64" s="9" t="n"/>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="9" t="n"/>
       <c r="F64" s="4" t="n">
         <v>2</v>
       </c>
@@ -2772,52 +2783,52 @@
       <c r="I64" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="4" t="inlineStr">
+      <c r="J64" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr"/>
       <c r="L64" s="4" t="inlineStr"/>
-      <c r="M64" s="8" t="n"/>
+      <c r="M64" s="9" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="8" t="n"/>
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="9" t="n">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="9" t="n"/>
+      <c r="C65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G65" s="10" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H65" s="11" t="inlineStr">
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama em todo o talude da curva da bacia</t>
         </is>
       </c>
-      <c r="I65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K65" s="9" t="inlineStr"/>
-      <c r="L65" s="9" t="inlineStr"/>
-      <c r="M65" s="8" t="n"/>
+      <c r="I65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr"/>
+      <c r="L65" s="10" t="inlineStr"/>
+      <c r="M65" s="9" t="n"/>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="12" t="n"/>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
+      <c r="A66" s="14" t="n"/>
+      <c r="B66" s="14" t="n"/>
+      <c r="C66" s="14" t="n"/>
+      <c r="D66" s="14" t="n"/>
+      <c r="E66" s="14" t="n"/>
       <c r="F66" s="4" t="n">
         <v>4</v>
       </c>
@@ -2834,72 +2845,72 @@
       <c r="I66" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J66" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K66" s="4" t="inlineStr"/>
       <c r="L66" s="4" t="inlineStr"/>
-      <c r="M66" s="12" t="n"/>
+      <c r="M66" s="14" t="n"/>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="9" t="n">
+      <c r="A67" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B67" s="13" t="inlineStr">
+      <c r="B67" s="15" t="inlineStr">
         <is>
           <t>Talude da Bacia — Curva (Escada 3)</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="10" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D67" s="13" t="inlineStr">
+      <c r="D67" s="15" t="inlineStr">
         <is>
           <t>Talude da Bacia — Curva (Escada 3)</t>
         </is>
       </c>
-      <c r="E67" s="9" t="n">
+      <c r="E67" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="10" t="inlineStr">
+      <c r="F67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H67" s="11" t="inlineStr">
+      <c r="H67" s="12" t="inlineStr">
         <is>
           <t>Remoção das gramas mal instaladas e deslocadas do talude</t>
         </is>
       </c>
-      <c r="I67" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K67" s="9" t="inlineStr"/>
-      <c r="L67" s="9" t="inlineStr"/>
-      <c r="M67" s="9" t="inlineStr">
+      <c r="I67" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr"/>
+      <c r="L67" s="10" t="inlineStr"/>
+      <c r="M67" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="8" t="n"/>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="9" t="n"/>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="9" t="n"/>
       <c r="F68" s="4" t="n">
         <v>2</v>
       </c>
@@ -2916,52 +2927,52 @@
       <c r="I68" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J68" s="4" t="inlineStr">
+      <c r="J68" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K68" s="4" t="inlineStr"/>
       <c r="L68" s="4" t="inlineStr"/>
-      <c r="M68" s="8" t="n"/>
+      <c r="M68" s="9" t="n"/>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="8" t="n"/>
-      <c r="B69" s="8" t="n"/>
-      <c r="C69" s="8" t="n"/>
-      <c r="D69" s="8" t="n"/>
-      <c r="E69" s="8" t="n"/>
-      <c r="F69" s="9" t="n">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="9" t="n"/>
+      <c r="C69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G69" s="10" t="inlineStr">
+      <c r="G69" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H69" s="11" t="inlineStr">
+      <c r="H69" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama em todo o talude da curva da bacia</t>
         </is>
       </c>
-      <c r="I69" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K69" s="9" t="inlineStr"/>
-      <c r="L69" s="9" t="inlineStr"/>
-      <c r="M69" s="8" t="n"/>
+      <c r="I69" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr"/>
+      <c r="L69" s="10" t="inlineStr"/>
+      <c r="M69" s="9" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="12" t="n"/>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
-      <c r="E70" s="12" t="n"/>
+      <c r="A70" s="14" t="n"/>
+      <c r="B70" s="14" t="n"/>
+      <c r="C70" s="14" t="n"/>
+      <c r="D70" s="14" t="n"/>
+      <c r="E70" s="14" t="n"/>
       <c r="F70" s="4" t="n">
         <v>4</v>
       </c>
@@ -2978,72 +2989,72 @@
       <c r="I70" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J70" s="4" t="inlineStr">
+      <c r="J70" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="4" t="inlineStr"/>
-      <c r="M70" s="12" t="n"/>
+      <c r="M70" s="14" t="n"/>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="9" t="n">
+      <c r="A71" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B71" s="13" t="inlineStr">
+      <c r="B71" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D71" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="E71" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H71" s="11" t="inlineStr">
+      <c r="E71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="inlineStr">
         <is>
           <t>Reaterro na face lateral da canaleta de 50cm</t>
         </is>
       </c>
-      <c r="I71" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K71" s="9" t="inlineStr"/>
-      <c r="L71" s="9" t="inlineStr"/>
-      <c r="M71" s="9" t="inlineStr">
+      <c r="I71" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr"/>
+      <c r="L71" s="10" t="inlineStr"/>
+      <c r="M71" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="8" t="n"/>
-      <c r="B72" s="8" t="n"/>
-      <c r="C72" s="8" t="n"/>
-      <c r="D72" s="8" t="n"/>
-      <c r="E72" s="8" t="n"/>
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="9" t="n"/>
+      <c r="C72" s="9" t="n"/>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="9" t="n"/>
       <c r="F72" s="4" t="n">
         <v>2</v>
       </c>
@@ -3060,52 +3071,52 @@
       <c r="I72" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J72" s="4" t="inlineStr">
+      <c r="J72" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K72" s="4" t="inlineStr"/>
       <c r="L72" s="4" t="inlineStr"/>
-      <c r="M72" s="8" t="n"/>
+      <c r="M72" s="9" t="n"/>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="8" t="n"/>
-      <c r="B73" s="8" t="n"/>
-      <c r="C73" s="8" t="n"/>
-      <c r="D73" s="8" t="n"/>
-      <c r="E73" s="8" t="n"/>
-      <c r="F73" s="9" t="n">
+      <c r="A73" s="9" t="n"/>
+      <c r="B73" s="9" t="n"/>
+      <c r="C73" s="9" t="n"/>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H73" s="11" t="inlineStr">
+      <c r="G73" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H73" s="12" t="inlineStr">
         <is>
           <t>Limpeza interna da canaleta (remoção de sedimento acumulado)</t>
         </is>
       </c>
-      <c r="I73" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K73" s="9" t="inlineStr"/>
-      <c r="L73" s="9" t="inlineStr"/>
-      <c r="M73" s="8" t="n"/>
+      <c r="I73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr"/>
+      <c r="L73" s="10" t="inlineStr"/>
+      <c r="M73" s="9" t="n"/>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="8" t="n"/>
-      <c r="B74" s="8" t="n"/>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="n"/>
+      <c r="A74" s="9" t="n"/>
+      <c r="B74" s="9" t="n"/>
+      <c r="C74" s="9" t="n"/>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="9" t="n"/>
       <c r="F74" s="4" t="n">
         <v>4</v>
       </c>
@@ -3122,52 +3133,52 @@
       <c r="I74" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="4" t="inlineStr"/>
-      <c r="M74" s="8" t="n"/>
+      <c r="M74" s="9" t="n"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="8" t="n"/>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="9" t="n">
+      <c r="A75" s="9" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H75" s="11" t="inlineStr">
+      <c r="G75" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H75" s="12" t="inlineStr">
         <is>
           <t>Acerto no nivelamento da crista da Berma</t>
         </is>
       </c>
-      <c r="I75" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K75" s="9" t="inlineStr"/>
-      <c r="L75" s="9" t="inlineStr"/>
-      <c r="M75" s="8" t="n"/>
+      <c r="I75" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr"/>
+      <c r="L75" s="10" t="inlineStr"/>
+      <c r="M75" s="9" t="n"/>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="8" t="n"/>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
-      <c r="E76" s="8" t="n"/>
+      <c r="A76" s="9" t="n"/>
+      <c r="B76" s="9" t="n"/>
+      <c r="C76" s="9" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
       <c r="F76" s="4" t="n">
         <v>6</v>
       </c>
@@ -3184,52 +3195,52 @@
       <c r="I76" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J76" s="4" t="inlineStr">
+      <c r="J76" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="4" t="inlineStr"/>
-      <c r="M76" s="8" t="n"/>
+      <c r="M76" s="9" t="n"/>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="8" t="n"/>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="9" t="n">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G77" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H77" s="11" t="inlineStr">
+      <c r="G77" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H77" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e nivelamento nos pontos de buraco/cavidade</t>
         </is>
       </c>
-      <c r="I77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K77" s="9" t="inlineStr"/>
-      <c r="L77" s="9" t="inlineStr"/>
-      <c r="M77" s="8" t="n"/>
+      <c r="I77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr"/>
+      <c r="L77" s="10" t="inlineStr"/>
+      <c r="M77" s="9" t="n"/>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="8" t="n"/>
-      <c r="B78" s="8" t="n"/>
-      <c r="C78" s="8" t="n"/>
-      <c r="D78" s="8" t="n"/>
-      <c r="E78" s="8" t="n"/>
+      <c r="A78" s="9" t="n"/>
+      <c r="B78" s="9" t="n"/>
+      <c r="C78" s="9" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
       <c r="F78" s="4" t="n">
         <v>8</v>
       </c>
@@ -3246,52 +3257,52 @@
       <c r="I78" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="J78" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K78" s="4" t="inlineStr"/>
       <c r="L78" s="4" t="inlineStr"/>
-      <c r="M78" s="8" t="n"/>
+      <c r="M78" s="9" t="n"/>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="8" t="n"/>
-      <c r="B79" s="8" t="n"/>
-      <c r="C79" s="8" t="n"/>
-      <c r="D79" s="8" t="n"/>
-      <c r="E79" s="8" t="n"/>
-      <c r="F79" s="9" t="n">
+      <c r="A79" s="9" t="n"/>
+      <c r="B79" s="9" t="n"/>
+      <c r="C79" s="9" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="G79" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H79" s="11" t="inlineStr">
+      <c r="G79" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H79" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama na Berma e berma externa</t>
         </is>
       </c>
-      <c r="I79" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K79" s="9" t="inlineStr"/>
-      <c r="L79" s="9" t="inlineStr"/>
-      <c r="M79" s="8" t="n"/>
+      <c r="I79" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr"/>
+      <c r="L79" s="10" t="inlineStr"/>
+      <c r="M79" s="9" t="n"/>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="8" t="n"/>
-      <c r="B80" s="8" t="n"/>
-      <c r="C80" s="8" t="n"/>
-      <c r="D80" s="8" t="n"/>
-      <c r="E80" s="8" t="n"/>
+      <c r="A80" s="9" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="9" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
       <c r="F80" s="4" t="n">
         <v>10</v>
       </c>
@@ -3308,45 +3319,45 @@
       <c r="I80" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J80" s="4" t="inlineStr">
+      <c r="J80" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="4" t="inlineStr"/>
-      <c r="M80" s="8" t="n"/>
+      <c r="M80" s="9" t="n"/>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="12" t="n"/>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="12" t="n"/>
-      <c r="F81" s="9" t="n">
+      <c r="A81" s="14" t="n"/>
+      <c r="B81" s="14" t="n"/>
+      <c r="C81" s="14" t="n"/>
+      <c r="D81" s="14" t="n"/>
+      <c r="E81" s="14" t="n"/>
+      <c r="F81" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="G81" s="10" t="inlineStr">
+      <c r="G81" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H81" s="11" t="inlineStr">
+      <c r="H81" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e organização da área</t>
         </is>
       </c>
-      <c r="I81" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J81" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K81" s="9" t="inlineStr"/>
-      <c r="L81" s="9" t="inlineStr"/>
-      <c r="M81" s="12" t="n"/>
+      <c r="I81" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr"/>
+      <c r="L81" s="10" t="inlineStr"/>
+      <c r="M81" s="14" t="n"/>
     </row>
     <row r="82" ht="16" customHeight="1">
       <c r="A82" s="4" t="n">
@@ -3386,56 +3397,56 @@
       <c r="I82" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J82" s="4" t="inlineStr">
+      <c r="J82" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="4" t="inlineStr"/>
-      <c r="M82" s="4" t="inlineStr">
+      <c r="M82" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="8" t="n"/>
-      <c r="B83" s="8" t="n"/>
-      <c r="C83" s="8" t="n"/>
-      <c r="D83" s="8" t="n"/>
-      <c r="E83" s="8" t="n"/>
-      <c r="F83" s="9" t="n">
+      <c r="A83" s="9" t="n"/>
+      <c r="B83" s="9" t="n"/>
+      <c r="C83" s="9" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G83" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H83" s="11" t="inlineStr">
+      <c r="G83" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H83" s="12" t="inlineStr">
         <is>
           <t>Recompactação do solo nas laterais da canaleta</t>
         </is>
       </c>
-      <c r="I83" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K83" s="9" t="inlineStr"/>
-      <c r="L83" s="9" t="inlineStr"/>
-      <c r="M83" s="8" t="n"/>
+      <c r="I83" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr"/>
+      <c r="L83" s="10" t="inlineStr"/>
+      <c r="M83" s="9" t="n"/>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="8" t="n"/>
-      <c r="B84" s="8" t="n"/>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
+      <c r="A84" s="9" t="n"/>
+      <c r="B84" s="9" t="n"/>
+      <c r="C84" s="9" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
       <c r="F84" s="4" t="n">
         <v>3</v>
       </c>
@@ -3452,52 +3463,52 @@
       <c r="I84" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J84" s="4" t="inlineStr">
+      <c r="J84" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr"/>
       <c r="L84" s="4" t="inlineStr"/>
-      <c r="M84" s="8" t="n"/>
+      <c r="M84" s="9" t="n"/>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="8" t="n"/>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="9" t="n">
+      <c r="A85" s="9" t="n"/>
+      <c r="B85" s="9" t="n"/>
+      <c r="C85" s="9" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G85" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H85" s="11" t="inlineStr">
+      <c r="G85" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H85" s="12" t="inlineStr">
         <is>
           <t>Aplicação de argamassa de regularização (traço 1:3) nas juntas</t>
         </is>
       </c>
-      <c r="I85" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J85" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K85" s="9" t="inlineStr"/>
-      <c r="L85" s="9" t="inlineStr"/>
-      <c r="M85" s="8" t="n"/>
+      <c r="I85" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K85" s="10" t="inlineStr"/>
+      <c r="L85" s="10" t="inlineStr"/>
+      <c r="M85" s="9" t="n"/>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="8" t="n"/>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="9" t="n"/>
+      <c r="C86" s="9" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
       <c r="F86" s="4" t="n">
         <v>5</v>
       </c>
@@ -3514,52 +3525,52 @@
       <c r="I86" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="J86" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr"/>
       <c r="L86" s="4" t="inlineStr"/>
-      <c r="M86" s="8" t="n"/>
+      <c r="M86" s="9" t="n"/>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="8" t="n"/>
-      <c r="B87" s="8" t="n"/>
-      <c r="C87" s="8" t="n"/>
-      <c r="D87" s="8" t="n"/>
-      <c r="E87" s="8" t="n"/>
-      <c r="F87" s="9" t="n">
+      <c r="A87" s="9" t="n"/>
+      <c r="B87" s="9" t="n"/>
+      <c r="C87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G87" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H87" s="11" t="inlineStr">
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H87" s="12" t="inlineStr">
         <is>
           <t>Remoção da grama sobre pontos de subsidência e buracos na Berma</t>
         </is>
       </c>
-      <c r="I87" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K87" s="9" t="inlineStr"/>
-      <c r="L87" s="9" t="inlineStr"/>
-      <c r="M87" s="8" t="n"/>
+      <c r="I87" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr"/>
+      <c r="L87" s="10" t="inlineStr"/>
+      <c r="M87" s="9" t="n"/>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="8" t="n"/>
-      <c r="B88" s="8" t="n"/>
-      <c r="C88" s="8" t="n"/>
-      <c r="D88" s="8" t="n"/>
-      <c r="E88" s="8" t="n"/>
+      <c r="A88" s="9" t="n"/>
+      <c r="B88" s="9" t="n"/>
+      <c r="C88" s="9" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
       <c r="F88" s="4" t="n">
         <v>7</v>
       </c>
@@ -3576,52 +3587,52 @@
       <c r="I88" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J88" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K88" s="4" t="inlineStr"/>
       <c r="L88" s="4" t="inlineStr"/>
-      <c r="M88" s="8" t="n"/>
+      <c r="M88" s="9" t="n"/>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="8" t="n"/>
-      <c r="B89" s="8" t="n"/>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="9" t="n">
+      <c r="A89" s="9" t="n"/>
+      <c r="B89" s="9" t="n"/>
+      <c r="C89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="G89" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H89" s="11" t="inlineStr">
+      <c r="G89" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H89" s="12" t="inlineStr">
         <is>
           <t>Compactação do solo nos pontos recompostos</t>
         </is>
       </c>
-      <c r="I89" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K89" s="9" t="inlineStr"/>
-      <c r="L89" s="9" t="inlineStr"/>
-      <c r="M89" s="8" t="n"/>
+      <c r="I89" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr"/>
+      <c r="L89" s="10" t="inlineStr"/>
+      <c r="M89" s="9" t="n"/>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="8" t="n"/>
-      <c r="B90" s="8" t="n"/>
-      <c r="C90" s="8" t="n"/>
-      <c r="D90" s="8" t="n"/>
-      <c r="E90" s="8" t="n"/>
+      <c r="A90" s="9" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="9" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
       <c r="F90" s="4" t="n">
         <v>9</v>
       </c>
@@ -3638,52 +3649,52 @@
       <c r="I90" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J90" s="4" t="inlineStr">
+      <c r="J90" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="4" t="inlineStr"/>
-      <c r="M90" s="8" t="n"/>
+      <c r="M90" s="9" t="n"/>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="8" t="n"/>
-      <c r="B91" s="8" t="n"/>
-      <c r="C91" s="8" t="n"/>
-      <c r="D91" s="8" t="n"/>
-      <c r="E91" s="8" t="n"/>
-      <c r="F91" s="9" t="n">
+      <c r="A91" s="9" t="n"/>
+      <c r="B91" s="9" t="n"/>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="G91" s="10" t="inlineStr">
+      <c r="G91" s="11" t="inlineStr">
         <is>
           <t>Macrodrenagem / 5S</t>
         </is>
       </c>
-      <c r="H91" s="11" t="inlineStr">
+      <c r="H91" s="12" t="inlineStr">
         <is>
           <t>Remoção do excedente de terra da berma</t>
         </is>
       </c>
-      <c r="I91" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K91" s="9" t="inlineStr"/>
-      <c r="L91" s="9" t="inlineStr"/>
-      <c r="M91" s="8" t="n"/>
+      <c r="I91" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr"/>
+      <c r="L91" s="10" t="inlineStr"/>
+      <c r="M91" s="9" t="n"/>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="12" t="n"/>
-      <c r="B92" s="12" t="n"/>
-      <c r="C92" s="12" t="n"/>
-      <c r="D92" s="12" t="n"/>
-      <c r="E92" s="12" t="n"/>
+      <c r="A92" s="14" t="n"/>
+      <c r="B92" s="14" t="n"/>
+      <c r="C92" s="14" t="n"/>
+      <c r="D92" s="14" t="n"/>
+      <c r="E92" s="14" t="n"/>
       <c r="F92" s="4" t="n">
         <v>11</v>
       </c>
@@ -3700,72 +3711,72 @@
       <c r="I92" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J92" s="4" t="inlineStr">
+      <c r="J92" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K92" s="4" t="inlineStr"/>
       <c r="L92" s="4" t="inlineStr"/>
-      <c r="M92" s="12" t="n"/>
+      <c r="M92" s="14" t="n"/>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="9" t="n">
+      <c r="A93" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B93" s="13" t="inlineStr">
+      <c r="B93" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="C93" s="9" t="inlineStr">
+      <c r="C93" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D93" s="13" t="inlineStr">
+      <c r="D93" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="E93" s="9" t="n">
+      <c r="E93" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F93" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H93" s="11" t="inlineStr">
+      <c r="F93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H93" s="12" t="inlineStr">
         <is>
           <t>Acerto no nivelamento da crista da Berma</t>
         </is>
       </c>
-      <c r="I93" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K93" s="9" t="inlineStr"/>
-      <c r="L93" s="9" t="inlineStr"/>
-      <c r="M93" s="9" t="inlineStr">
+      <c r="I93" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J93" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K93" s="10" t="inlineStr"/>
+      <c r="L93" s="10" t="inlineStr"/>
+      <c r="M93" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="8" t="n"/>
-      <c r="B94" s="8" t="n"/>
-      <c r="C94" s="8" t="n"/>
-      <c r="D94" s="8" t="n"/>
-      <c r="E94" s="8" t="n"/>
+      <c r="A94" s="9" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
       <c r="F94" s="4" t="n">
         <v>2</v>
       </c>
@@ -3782,52 +3793,52 @@
       <c r="I94" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J94" s="4" t="inlineStr">
+      <c r="J94" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K94" s="4" t="inlineStr"/>
       <c r="L94" s="4" t="inlineStr"/>
-      <c r="M94" s="8" t="n"/>
+      <c r="M94" s="9" t="n"/>
     </row>
     <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="8" t="n"/>
-      <c r="B95" s="8" t="n"/>
-      <c r="C95" s="8" t="n"/>
-      <c r="D95" s="8" t="n"/>
-      <c r="E95" s="8" t="n"/>
-      <c r="F95" s="9" t="n">
+      <c r="A95" s="9" t="n"/>
+      <c r="B95" s="9" t="n"/>
+      <c r="C95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G95" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H95" s="11" t="inlineStr">
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H95" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e nivelamento nos pontos de buraco/cavidade</t>
         </is>
       </c>
-      <c r="I95" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K95" s="9" t="inlineStr"/>
-      <c r="L95" s="9" t="inlineStr"/>
-      <c r="M95" s="8" t="n"/>
+      <c r="I95" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K95" s="10" t="inlineStr"/>
+      <c r="L95" s="10" t="inlineStr"/>
+      <c r="M95" s="9" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="8" t="n"/>
-      <c r="B96" s="8" t="n"/>
-      <c r="C96" s="8" t="n"/>
-      <c r="D96" s="8" t="n"/>
-      <c r="E96" s="8" t="n"/>
+      <c r="A96" s="9" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
       <c r="F96" s="4" t="n">
         <v>4</v>
       </c>
@@ -3844,52 +3855,52 @@
       <c r="I96" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J96" s="4" t="inlineStr">
+      <c r="J96" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K96" s="4" t="inlineStr"/>
       <c r="L96" s="4" t="inlineStr"/>
-      <c r="M96" s="8" t="n"/>
+      <c r="M96" s="9" t="n"/>
     </row>
     <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="8" t="n"/>
-      <c r="B97" s="8" t="n"/>
-      <c r="C97" s="8" t="n"/>
-      <c r="D97" s="8" t="n"/>
-      <c r="E97" s="8" t="n"/>
-      <c r="F97" s="9" t="n">
+      <c r="A97" s="9" t="n"/>
+      <c r="B97" s="9" t="n"/>
+      <c r="C97" s="9" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G97" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H97" s="11" t="inlineStr">
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H97" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama na Berma e berma externa</t>
         </is>
       </c>
-      <c r="I97" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J97" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K97" s="9" t="inlineStr"/>
-      <c r="L97" s="9" t="inlineStr"/>
-      <c r="M97" s="8" t="n"/>
+      <c r="I97" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J97" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K97" s="10" t="inlineStr"/>
+      <c r="L97" s="10" t="inlineStr"/>
+      <c r="M97" s="9" t="n"/>
     </row>
     <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="8" t="n"/>
-      <c r="B98" s="8" t="n"/>
-      <c r="C98" s="8" t="n"/>
-      <c r="D98" s="8" t="n"/>
-      <c r="E98" s="8" t="n"/>
+      <c r="A98" s="9" t="n"/>
+      <c r="B98" s="9" t="n"/>
+      <c r="C98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
       <c r="F98" s="4" t="n">
         <v>6</v>
       </c>
@@ -3906,45 +3917,45 @@
       <c r="I98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J98" s="4" t="inlineStr">
+      <c r="J98" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K98" s="4" t="inlineStr"/>
       <c r="L98" s="4" t="inlineStr"/>
-      <c r="M98" s="8" t="n"/>
+      <c r="M98" s="9" t="n"/>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="12" t="n"/>
-      <c r="B99" s="12" t="n"/>
-      <c r="C99" s="12" t="n"/>
-      <c r="D99" s="12" t="n"/>
-      <c r="E99" s="12" t="n"/>
-      <c r="F99" s="9" t="n">
+      <c r="A99" s="14" t="n"/>
+      <c r="B99" s="14" t="n"/>
+      <c r="C99" s="14" t="n"/>
+      <c r="D99" s="14" t="n"/>
+      <c r="E99" s="14" t="n"/>
+      <c r="F99" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G99" s="10" t="inlineStr">
+      <c r="G99" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H99" s="11" t="inlineStr">
+      <c r="H99" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e organização da área</t>
         </is>
       </c>
-      <c r="I99" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J99" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K99" s="9" t="inlineStr"/>
-      <c r="L99" s="9" t="inlineStr"/>
-      <c r="M99" s="12" t="n"/>
+      <c r="I99" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J99" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K99" s="10" t="inlineStr"/>
+      <c r="L99" s="10" t="inlineStr"/>
+      <c r="M99" s="14" t="n"/>
     </row>
     <row r="100" ht="16" customHeight="1">
       <c r="A100" s="4" t="n">
@@ -3984,56 +3995,56 @@
       <c r="I100" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
+      <c r="J100" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K100" s="4" t="inlineStr"/>
       <c r="L100" s="4" t="inlineStr"/>
-      <c r="M100" s="4" t="inlineStr">
+      <c r="M100" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="8" t="n"/>
-      <c r="B101" s="8" t="n"/>
-      <c r="C101" s="8" t="n"/>
-      <c r="D101" s="8" t="n"/>
-      <c r="E101" s="8" t="n"/>
-      <c r="F101" s="9" t="n">
+      <c r="A101" s="9" t="n"/>
+      <c r="B101" s="9" t="n"/>
+      <c r="C101" s="9" t="n"/>
+      <c r="D101" s="9" t="n"/>
+      <c r="E101" s="9" t="n"/>
+      <c r="F101" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G101" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H101" s="11" t="inlineStr">
+      <c r="G101" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H101" s="12" t="inlineStr">
         <is>
           <t>Recompactação do solo nas laterais da canaleta</t>
         </is>
       </c>
-      <c r="I101" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J101" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K101" s="9" t="inlineStr"/>
-      <c r="L101" s="9" t="inlineStr"/>
-      <c r="M101" s="8" t="n"/>
+      <c r="I101" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J101" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr"/>
+      <c r="L101" s="10" t="inlineStr"/>
+      <c r="M101" s="9" t="n"/>
     </row>
     <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="8" t="n"/>
-      <c r="B102" s="8" t="n"/>
-      <c r="C102" s="8" t="n"/>
-      <c r="D102" s="8" t="n"/>
-      <c r="E102" s="8" t="n"/>
+      <c r="A102" s="9" t="n"/>
+      <c r="B102" s="9" t="n"/>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
       <c r="F102" s="4" t="n">
         <v>3</v>
       </c>
@@ -4050,52 +4061,52 @@
       <c r="I102" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J102" s="4" t="inlineStr">
+      <c r="J102" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr"/>
       <c r="L102" s="4" t="inlineStr"/>
-      <c r="M102" s="8" t="n"/>
+      <c r="M102" s="9" t="n"/>
     </row>
     <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="8" t="n"/>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="9" t="n">
+      <c r="A103" s="9" t="n"/>
+      <c r="B103" s="9" t="n"/>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G103" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H103" s="11" t="inlineStr">
+      <c r="G103" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H103" s="12" t="inlineStr">
         <is>
           <t>Aplicação de argamassa de regularização (traço 1:3) nas juntas</t>
         </is>
       </c>
-      <c r="I103" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J103" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K103" s="9" t="inlineStr"/>
-      <c r="L103" s="9" t="inlineStr"/>
-      <c r="M103" s="8" t="n"/>
+      <c r="I103" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J103" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K103" s="10" t="inlineStr"/>
+      <c r="L103" s="10" t="inlineStr"/>
+      <c r="M103" s="9" t="n"/>
     </row>
     <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="8" t="n"/>
-      <c r="B104" s="8" t="n"/>
-      <c r="C104" s="8" t="n"/>
-      <c r="D104" s="8" t="n"/>
-      <c r="E104" s="8" t="n"/>
+      <c r="A104" s="9" t="n"/>
+      <c r="B104" s="9" t="n"/>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="9" t="n"/>
       <c r="F104" s="4" t="n">
         <v>5</v>
       </c>
@@ -4112,52 +4123,52 @@
       <c r="I104" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="J104" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K104" s="4" t="inlineStr"/>
       <c r="L104" s="4" t="inlineStr"/>
-      <c r="M104" s="8" t="n"/>
+      <c r="M104" s="9" t="n"/>
     </row>
     <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="8" t="n"/>
-      <c r="B105" s="8" t="n"/>
-      <c r="C105" s="8" t="n"/>
-      <c r="D105" s="8" t="n"/>
-      <c r="E105" s="8" t="n"/>
-      <c r="F105" s="9" t="n">
+      <c r="A105" s="9" t="n"/>
+      <c r="B105" s="9" t="n"/>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G105" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H105" s="11" t="inlineStr">
+      <c r="G105" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H105" s="12" t="inlineStr">
         <is>
           <t>Remoção da grama sobre pontos de subsidência e buracos na Berma</t>
         </is>
       </c>
-      <c r="I105" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J105" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K105" s="9" t="inlineStr"/>
-      <c r="L105" s="9" t="inlineStr"/>
-      <c r="M105" s="8" t="n"/>
+      <c r="I105" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J105" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K105" s="10" t="inlineStr"/>
+      <c r="L105" s="10" t="inlineStr"/>
+      <c r="M105" s="9" t="n"/>
     </row>
     <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="8" t="n"/>
-      <c r="B106" s="8" t="n"/>
-      <c r="C106" s="8" t="n"/>
-      <c r="D106" s="8" t="n"/>
-      <c r="E106" s="8" t="n"/>
+      <c r="A106" s="9" t="n"/>
+      <c r="B106" s="9" t="n"/>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
       <c r="F106" s="4" t="n">
         <v>7</v>
       </c>
@@ -4174,52 +4185,52 @@
       <c r="I106" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="J106" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K106" s="4" t="inlineStr"/>
       <c r="L106" s="4" t="inlineStr"/>
-      <c r="M106" s="8" t="n"/>
+      <c r="M106" s="9" t="n"/>
     </row>
     <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="8" t="n"/>
-      <c r="B107" s="8" t="n"/>
-      <c r="C107" s="8" t="n"/>
-      <c r="D107" s="8" t="n"/>
-      <c r="E107" s="8" t="n"/>
-      <c r="F107" s="9" t="n">
+      <c r="A107" s="9" t="n"/>
+      <c r="B107" s="9" t="n"/>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="9" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="G107" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H107" s="11" t="inlineStr">
+      <c r="G107" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr">
         <is>
           <t>Compactação do solo nos pontos recompostos</t>
         </is>
       </c>
-      <c r="I107" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J107" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K107" s="9" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr"/>
-      <c r="M107" s="8" t="n"/>
+      <c r="I107" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J107" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K107" s="10" t="inlineStr"/>
+      <c r="L107" s="10" t="inlineStr"/>
+      <c r="M107" s="9" t="n"/>
     </row>
     <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="8" t="n"/>
-      <c r="B108" s="8" t="n"/>
-      <c r="C108" s="8" t="n"/>
-      <c r="D108" s="8" t="n"/>
-      <c r="E108" s="8" t="n"/>
+      <c r="A108" s="9" t="n"/>
+      <c r="B108" s="9" t="n"/>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="9" t="n"/>
+      <c r="E108" s="9" t="n"/>
       <c r="F108" s="4" t="n">
         <v>9</v>
       </c>
@@ -4236,52 +4247,52 @@
       <c r="I108" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J108" s="4" t="inlineStr">
+      <c r="J108" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="4" t="inlineStr"/>
-      <c r="M108" s="8" t="n"/>
+      <c r="M108" s="9" t="n"/>
     </row>
     <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="8" t="n"/>
-      <c r="B109" s="8" t="n"/>
-      <c r="C109" s="8" t="n"/>
-      <c r="D109" s="8" t="n"/>
-      <c r="E109" s="8" t="n"/>
-      <c r="F109" s="9" t="n">
+      <c r="A109" s="9" t="n"/>
+      <c r="B109" s="9" t="n"/>
+      <c r="C109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="G109" s="10" t="inlineStr">
+      <c r="G109" s="11" t="inlineStr">
         <is>
           <t>Macrodrenagem / 5S</t>
         </is>
       </c>
-      <c r="H109" s="11" t="inlineStr">
+      <c r="H109" s="12" t="inlineStr">
         <is>
           <t>Remoção do excedente de terra da berma</t>
         </is>
       </c>
-      <c r="I109" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J109" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr"/>
-      <c r="M109" s="8" t="n"/>
+      <c r="I109" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J109" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K109" s="10" t="inlineStr"/>
+      <c r="L109" s="10" t="inlineStr"/>
+      <c r="M109" s="9" t="n"/>
     </row>
     <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="12" t="n"/>
-      <c r="B110" s="12" t="n"/>
-      <c r="C110" s="12" t="n"/>
-      <c r="D110" s="12" t="n"/>
-      <c r="E110" s="12" t="n"/>
+      <c r="A110" s="14" t="n"/>
+      <c r="B110" s="14" t="n"/>
+      <c r="C110" s="14" t="n"/>
+      <c r="D110" s="14" t="n"/>
+      <c r="E110" s="14" t="n"/>
       <c r="F110" s="4" t="n">
         <v>11</v>
       </c>
@@ -4298,72 +4309,72 @@
       <c r="I110" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J110" s="4" t="inlineStr">
+      <c r="J110" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K110" s="4" t="inlineStr"/>
       <c r="L110" s="4" t="inlineStr"/>
-      <c r="M110" s="12" t="n"/>
+      <c r="M110" s="14" t="n"/>
     </row>
     <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="9" t="n">
+      <c r="A111" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B111" s="13" t="inlineStr">
+      <c r="B111" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="C111" s="9" t="inlineStr">
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D111" s="13" t="inlineStr">
+      <c r="D111" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="E111" s="9" t="n">
+      <c r="E111" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="F111" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G111" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H111" s="11" t="inlineStr">
+      <c r="F111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H111" s="12" t="inlineStr">
         <is>
           <t>Acerto no nivelamento da crista da Berma</t>
         </is>
       </c>
-      <c r="I111" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K111" s="9" t="inlineStr"/>
-      <c r="L111" s="9" t="inlineStr"/>
-      <c r="M111" s="9" t="inlineStr">
+      <c r="I111" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J111" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K111" s="10" t="inlineStr"/>
+      <c r="L111" s="10" t="inlineStr"/>
+      <c r="M111" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="112" ht="16" customHeight="1">
-      <c r="A112" s="8" t="n"/>
-      <c r="B112" s="8" t="n"/>
-      <c r="C112" s="8" t="n"/>
-      <c r="D112" s="8" t="n"/>
-      <c r="E112" s="8" t="n"/>
+      <c r="A112" s="9" t="n"/>
+      <c r="B112" s="9" t="n"/>
+      <c r="C112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
       <c r="F112" s="4" t="n">
         <v>2</v>
       </c>
@@ -4380,52 +4391,52 @@
       <c r="I112" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J112" s="4" t="inlineStr">
+      <c r="J112" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K112" s="4" t="inlineStr"/>
       <c r="L112" s="4" t="inlineStr"/>
-      <c r="M112" s="8" t="n"/>
+      <c r="M112" s="9" t="n"/>
     </row>
     <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="8" t="n"/>
-      <c r="B113" s="8" t="n"/>
-      <c r="C113" s="8" t="n"/>
-      <c r="D113" s="8" t="n"/>
-      <c r="E113" s="8" t="n"/>
-      <c r="F113" s="9" t="n">
+      <c r="A113" s="9" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="9" t="n"/>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G113" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H113" s="11" t="inlineStr">
+      <c r="G113" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e nivelamento nos pontos de buraco/cavidade</t>
         </is>
       </c>
-      <c r="I113" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K113" s="9" t="inlineStr"/>
-      <c r="L113" s="9" t="inlineStr"/>
-      <c r="M113" s="8" t="n"/>
+      <c r="I113" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J113" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K113" s="10" t="inlineStr"/>
+      <c r="L113" s="10" t="inlineStr"/>
+      <c r="M113" s="9" t="n"/>
     </row>
     <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="8" t="n"/>
-      <c r="B114" s="8" t="n"/>
-      <c r="C114" s="8" t="n"/>
-      <c r="D114" s="8" t="n"/>
-      <c r="E114" s="8" t="n"/>
+      <c r="A114" s="9" t="n"/>
+      <c r="B114" s="9" t="n"/>
+      <c r="C114" s="9" t="n"/>
+      <c r="D114" s="9" t="n"/>
+      <c r="E114" s="9" t="n"/>
       <c r="F114" s="4" t="n">
         <v>4</v>
       </c>
@@ -4442,52 +4453,52 @@
       <c r="I114" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J114" s="4" t="inlineStr">
+      <c r="J114" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K114" s="4" t="inlineStr"/>
       <c r="L114" s="4" t="inlineStr"/>
-      <c r="M114" s="8" t="n"/>
+      <c r="M114" s="9" t="n"/>
     </row>
     <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="8" t="n"/>
-      <c r="B115" s="8" t="n"/>
-      <c r="C115" s="8" t="n"/>
-      <c r="D115" s="8" t="n"/>
-      <c r="E115" s="8" t="n"/>
-      <c r="F115" s="9" t="n">
+      <c r="A115" s="9" t="n"/>
+      <c r="B115" s="9" t="n"/>
+      <c r="C115" s="9" t="n"/>
+      <c r="D115" s="9" t="n"/>
+      <c r="E115" s="9" t="n"/>
+      <c r="F115" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G115" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H115" s="11" t="inlineStr">
+      <c r="G115" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama na Berma e berma externa</t>
         </is>
       </c>
-      <c r="I115" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J115" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K115" s="9" t="inlineStr"/>
-      <c r="L115" s="9" t="inlineStr"/>
-      <c r="M115" s="8" t="n"/>
+      <c r="I115" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J115" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K115" s="10" t="inlineStr"/>
+      <c r="L115" s="10" t="inlineStr"/>
+      <c r="M115" s="9" t="n"/>
     </row>
     <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="8" t="n"/>
-      <c r="B116" s="8" t="n"/>
-      <c r="C116" s="8" t="n"/>
-      <c r="D116" s="8" t="n"/>
-      <c r="E116" s="8" t="n"/>
+      <c r="A116" s="9" t="n"/>
+      <c r="B116" s="9" t="n"/>
+      <c r="C116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
       <c r="F116" s="4" t="n">
         <v>6</v>
       </c>
@@ -4504,45 +4515,45 @@
       <c r="I116" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J116" s="4" t="inlineStr">
+      <c r="J116" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr"/>
       <c r="L116" s="4" t="inlineStr"/>
-      <c r="M116" s="8" t="n"/>
+      <c r="M116" s="9" t="n"/>
     </row>
     <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="12" t="n"/>
-      <c r="B117" s="12" t="n"/>
-      <c r="C117" s="12" t="n"/>
-      <c r="D117" s="12" t="n"/>
-      <c r="E117" s="12" t="n"/>
-      <c r="F117" s="9" t="n">
+      <c r="A117" s="14" t="n"/>
+      <c r="B117" s="14" t="n"/>
+      <c r="C117" s="14" t="n"/>
+      <c r="D117" s="14" t="n"/>
+      <c r="E117" s="14" t="n"/>
+      <c r="F117" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G117" s="10" t="inlineStr">
+      <c r="G117" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H117" s="11" t="inlineStr">
+      <c r="H117" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e organização da área</t>
         </is>
       </c>
-      <c r="I117" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J117" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K117" s="9" t="inlineStr"/>
-      <c r="L117" s="9" t="inlineStr"/>
-      <c r="M117" s="12" t="n"/>
+      <c r="I117" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K117" s="10" t="inlineStr"/>
+      <c r="L117" s="10" t="inlineStr"/>
+      <c r="M117" s="14" t="n"/>
     </row>
     <row r="118" ht="16" customHeight="1">
       <c r="A118" s="4" t="n">
@@ -4582,56 +4593,56 @@
       <c r="I118" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="4" t="inlineStr">
+      <c r="J118" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
       <c r="L118" s="4" t="inlineStr"/>
-      <c r="M118" s="4" t="inlineStr">
+      <c r="M118" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="8" t="n"/>
-      <c r="B119" s="8" t="n"/>
-      <c r="C119" s="8" t="n"/>
-      <c r="D119" s="8" t="n"/>
-      <c r="E119" s="8" t="n"/>
-      <c r="F119" s="9" t="n">
+      <c r="A119" s="9" t="n"/>
+      <c r="B119" s="9" t="n"/>
+      <c r="C119" s="9" t="n"/>
+      <c r="D119" s="9" t="n"/>
+      <c r="E119" s="9" t="n"/>
+      <c r="F119" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G119" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H119" s="11" t="inlineStr">
+      <c r="G119" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
         <is>
           <t>Remoção da grama sobre pontos de subsidência e buracos na Berma</t>
         </is>
       </c>
-      <c r="I119" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J119" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K119" s="9" t="inlineStr"/>
-      <c r="L119" s="9" t="inlineStr"/>
-      <c r="M119" s="8" t="n"/>
+      <c r="I119" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K119" s="10" t="inlineStr"/>
+      <c r="L119" s="10" t="inlineStr"/>
+      <c r="M119" s="9" t="n"/>
     </row>
     <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="8" t="n"/>
-      <c r="B120" s="8" t="n"/>
-      <c r="C120" s="8" t="n"/>
-      <c r="D120" s="8" t="n"/>
-      <c r="E120" s="8" t="n"/>
+      <c r="A120" s="9" t="n"/>
+      <c r="B120" s="9" t="n"/>
+      <c r="C120" s="9" t="n"/>
+      <c r="D120" s="9" t="n"/>
+      <c r="E120" s="9" t="n"/>
       <c r="F120" s="4" t="n">
         <v>3</v>
       </c>
@@ -4648,52 +4659,52 @@
       <c r="I120" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J120" s="4" t="inlineStr">
+      <c r="J120" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K120" s="4" t="inlineStr"/>
       <c r="L120" s="4" t="inlineStr"/>
-      <c r="M120" s="8" t="n"/>
+      <c r="M120" s="9" t="n"/>
     </row>
     <row r="121" ht="16" customHeight="1">
-      <c r="A121" s="8" t="n"/>
-      <c r="B121" s="8" t="n"/>
-      <c r="C121" s="8" t="n"/>
-      <c r="D121" s="8" t="n"/>
-      <c r="E121" s="8" t="n"/>
-      <c r="F121" s="9" t="n">
+      <c r="A121" s="9" t="n"/>
+      <c r="B121" s="9" t="n"/>
+      <c r="C121" s="9" t="n"/>
+      <c r="D121" s="9" t="n"/>
+      <c r="E121" s="9" t="n"/>
+      <c r="F121" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G121" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H121" s="11" t="inlineStr">
+      <c r="G121" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
         <is>
           <t>Compactação do solo nos pontos recompostos</t>
         </is>
       </c>
-      <c r="I121" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K121" s="9" t="inlineStr"/>
-      <c r="L121" s="9" t="inlineStr"/>
-      <c r="M121" s="8" t="n"/>
+      <c r="I121" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K121" s="10" t="inlineStr"/>
+      <c r="L121" s="10" t="inlineStr"/>
+      <c r="M121" s="9" t="n"/>
     </row>
     <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="8" t="n"/>
-      <c r="B122" s="8" t="n"/>
-      <c r="C122" s="8" t="n"/>
-      <c r="D122" s="8" t="n"/>
-      <c r="E122" s="8" t="n"/>
+      <c r="A122" s="9" t="n"/>
+      <c r="B122" s="9" t="n"/>
+      <c r="C122" s="9" t="n"/>
+      <c r="D122" s="9" t="n"/>
+      <c r="E122" s="9" t="n"/>
       <c r="F122" s="4" t="n">
         <v>5</v>
       </c>
@@ -4710,52 +4721,52 @@
       <c r="I122" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J122" s="4" t="inlineStr">
+      <c r="J122" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K122" s="4" t="inlineStr"/>
       <c r="L122" s="4" t="inlineStr"/>
-      <c r="M122" s="8" t="n"/>
+      <c r="M122" s="9" t="n"/>
     </row>
     <row r="123" ht="16" customHeight="1">
-      <c r="A123" s="8" t="n"/>
-      <c r="B123" s="8" t="n"/>
-      <c r="C123" s="8" t="n"/>
-      <c r="D123" s="8" t="n"/>
-      <c r="E123" s="8" t="n"/>
-      <c r="F123" s="9" t="n">
+      <c r="A123" s="9" t="n"/>
+      <c r="B123" s="9" t="n"/>
+      <c r="C123" s="9" t="n"/>
+      <c r="D123" s="9" t="n"/>
+      <c r="E123" s="9" t="n"/>
+      <c r="F123" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G123" s="10" t="inlineStr">
+      <c r="G123" s="11" t="inlineStr">
         <is>
           <t>Macrodrenagem / 5S</t>
         </is>
       </c>
-      <c r="H123" s="11" t="inlineStr">
+      <c r="H123" s="12" t="inlineStr">
         <is>
           <t>Remoção do excedente de terra da berma</t>
         </is>
       </c>
-      <c r="I123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K123" s="9" t="inlineStr"/>
-      <c r="L123" s="9" t="inlineStr"/>
-      <c r="M123" s="8" t="n"/>
+      <c r="I123" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J123" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K123" s="10" t="inlineStr"/>
+      <c r="L123" s="10" t="inlineStr"/>
+      <c r="M123" s="9" t="n"/>
     </row>
     <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="12" t="n"/>
-      <c r="B124" s="12" t="n"/>
-      <c r="C124" s="12" t="n"/>
-      <c r="D124" s="12" t="n"/>
-      <c r="E124" s="12" t="n"/>
+      <c r="A124" s="14" t="n"/>
+      <c r="B124" s="14" t="n"/>
+      <c r="C124" s="14" t="n"/>
+      <c r="D124" s="14" t="n"/>
+      <c r="E124" s="14" t="n"/>
       <c r="F124" s="4" t="n">
         <v>7</v>
       </c>
@@ -4772,72 +4783,72 @@
       <c r="I124" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J124" s="4" t="inlineStr">
+      <c r="J124" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K124" s="4" t="inlineStr"/>
       <c r="L124" s="4" t="inlineStr"/>
-      <c r="M124" s="12" t="n"/>
+      <c r="M124" s="14" t="n"/>
     </row>
     <row r="125" ht="16" customHeight="1">
-      <c r="A125" s="9" t="n">
+      <c r="A125" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B125" s="13" t="inlineStr">
+      <c r="B125" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="C125" s="9" t="inlineStr">
+      <c r="C125" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D125" s="13" t="inlineStr">
+      <c r="D125" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="E125" s="9" t="n">
+      <c r="E125" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="F125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G125" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H125" s="11" t="inlineStr">
+      <c r="F125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H125" s="12" t="inlineStr">
         <is>
           <t>Reaterro na face lateral da canaleta de 50cm</t>
         </is>
       </c>
-      <c r="I125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J125" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K125" s="9" t="inlineStr"/>
-      <c r="L125" s="9" t="inlineStr"/>
-      <c r="M125" s="9" t="inlineStr">
+      <c r="I125" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J125" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K125" s="10" t="inlineStr"/>
+      <c r="L125" s="10" t="inlineStr"/>
+      <c r="M125" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="126" ht="16" customHeight="1">
-      <c r="A126" s="8" t="n"/>
-      <c r="B126" s="8" t="n"/>
-      <c r="C126" s="8" t="n"/>
-      <c r="D126" s="8" t="n"/>
-      <c r="E126" s="8" t="n"/>
+      <c r="A126" s="9" t="n"/>
+      <c r="B126" s="9" t="n"/>
+      <c r="C126" s="9" t="n"/>
+      <c r="D126" s="9" t="n"/>
+      <c r="E126" s="9" t="n"/>
       <c r="F126" s="4" t="n">
         <v>2</v>
       </c>
@@ -4854,52 +4865,52 @@
       <c r="I126" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J126" s="4" t="inlineStr">
+      <c r="J126" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr"/>
       <c r="L126" s="4" t="inlineStr"/>
-      <c r="M126" s="8" t="n"/>
+      <c r="M126" s="9" t="n"/>
     </row>
     <row r="127" ht="16" customHeight="1">
-      <c r="A127" s="8" t="n"/>
-      <c r="B127" s="8" t="n"/>
-      <c r="C127" s="8" t="n"/>
-      <c r="D127" s="8" t="n"/>
-      <c r="E127" s="8" t="n"/>
-      <c r="F127" s="9" t="n">
+      <c r="A127" s="9" t="n"/>
+      <c r="B127" s="9" t="n"/>
+      <c r="C127" s="9" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G127" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H127" s="11" t="inlineStr">
+      <c r="G127" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H127" s="12" t="inlineStr">
         <is>
           <t>Limpeza interna da canaleta (remoção de sedimento acumulado)</t>
         </is>
       </c>
-      <c r="I127" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J127" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K127" s="9" t="inlineStr"/>
-      <c r="L127" s="9" t="inlineStr"/>
-      <c r="M127" s="8" t="n"/>
+      <c r="I127" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J127" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K127" s="10" t="inlineStr"/>
+      <c r="L127" s="10" t="inlineStr"/>
+      <c r="M127" s="9" t="n"/>
     </row>
     <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="8" t="n"/>
-      <c r="B128" s="8" t="n"/>
-      <c r="C128" s="8" t="n"/>
-      <c r="D128" s="8" t="n"/>
-      <c r="E128" s="8" t="n"/>
+      <c r="A128" s="9" t="n"/>
+      <c r="B128" s="9" t="n"/>
+      <c r="C128" s="9" t="n"/>
+      <c r="D128" s="9" t="n"/>
+      <c r="E128" s="9" t="n"/>
       <c r="F128" s="4" t="n">
         <v>4</v>
       </c>
@@ -4916,52 +4927,52 @@
       <c r="I128" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J128" s="4" t="inlineStr">
+      <c r="J128" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K128" s="4" t="inlineStr"/>
       <c r="L128" s="4" t="inlineStr"/>
-      <c r="M128" s="8" t="n"/>
+      <c r="M128" s="9" t="n"/>
     </row>
     <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="8" t="n"/>
-      <c r="B129" s="8" t="n"/>
-      <c r="C129" s="8" t="n"/>
-      <c r="D129" s="8" t="n"/>
-      <c r="E129" s="8" t="n"/>
-      <c r="F129" s="9" t="n">
+      <c r="A129" s="9" t="n"/>
+      <c r="B129" s="9" t="n"/>
+      <c r="C129" s="9" t="n"/>
+      <c r="D129" s="9" t="n"/>
+      <c r="E129" s="9" t="n"/>
+      <c r="F129" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G129" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H129" s="11" t="inlineStr">
+      <c r="G129" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
         <is>
           <t>Acerto no nivelamento da crista da Berma</t>
         </is>
       </c>
-      <c r="I129" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J129" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K129" s="9" t="inlineStr"/>
-      <c r="L129" s="9" t="inlineStr"/>
-      <c r="M129" s="8" t="n"/>
+      <c r="I129" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J129" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K129" s="10" t="inlineStr"/>
+      <c r="L129" s="10" t="inlineStr"/>
+      <c r="M129" s="9" t="n"/>
     </row>
     <row r="130" ht="16" customHeight="1">
-      <c r="A130" s="8" t="n"/>
-      <c r="B130" s="8" t="n"/>
-      <c r="C130" s="8" t="n"/>
-      <c r="D130" s="8" t="n"/>
-      <c r="E130" s="8" t="n"/>
+      <c r="A130" s="9" t="n"/>
+      <c r="B130" s="9" t="n"/>
+      <c r="C130" s="9" t="n"/>
+      <c r="D130" s="9" t="n"/>
+      <c r="E130" s="9" t="n"/>
       <c r="F130" s="4" t="n">
         <v>6</v>
       </c>
@@ -4978,52 +4989,52 @@
       <c r="I130" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J130" s="4" t="inlineStr">
+      <c r="J130" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K130" s="4" t="inlineStr"/>
       <c r="L130" s="4" t="inlineStr"/>
-      <c r="M130" s="8" t="n"/>
+      <c r="M130" s="9" t="n"/>
     </row>
     <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="8" t="n"/>
-      <c r="B131" s="8" t="n"/>
-      <c r="C131" s="8" t="n"/>
-      <c r="D131" s="8" t="n"/>
-      <c r="E131" s="8" t="n"/>
-      <c r="F131" s="9" t="n">
+      <c r="A131" s="9" t="n"/>
+      <c r="B131" s="9" t="n"/>
+      <c r="C131" s="9" t="n"/>
+      <c r="D131" s="9" t="n"/>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G131" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H131" s="11" t="inlineStr">
+      <c r="G131" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H131" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e nivelamento nos pontos de buraco/cavidade</t>
         </is>
       </c>
-      <c r="I131" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K131" s="9" t="inlineStr"/>
-      <c r="L131" s="9" t="inlineStr"/>
-      <c r="M131" s="8" t="n"/>
+      <c r="I131" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J131" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K131" s="10" t="inlineStr"/>
+      <c r="L131" s="10" t="inlineStr"/>
+      <c r="M131" s="9" t="n"/>
     </row>
     <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="8" t="n"/>
-      <c r="B132" s="8" t="n"/>
-      <c r="C132" s="8" t="n"/>
-      <c r="D132" s="8" t="n"/>
-      <c r="E132" s="8" t="n"/>
+      <c r="A132" s="9" t="n"/>
+      <c r="B132" s="9" t="n"/>
+      <c r="C132" s="9" t="n"/>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
       <c r="F132" s="4" t="n">
         <v>8</v>
       </c>
@@ -5040,52 +5051,52 @@
       <c r="I132" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J132" s="4" t="inlineStr">
+      <c r="J132" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K132" s="4" t="inlineStr"/>
       <c r="L132" s="4" t="inlineStr"/>
-      <c r="M132" s="8" t="n"/>
+      <c r="M132" s="9" t="n"/>
     </row>
     <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="8" t="n"/>
-      <c r="B133" s="8" t="n"/>
-      <c r="C133" s="8" t="n"/>
-      <c r="D133" s="8" t="n"/>
-      <c r="E133" s="8" t="n"/>
-      <c r="F133" s="9" t="n">
+      <c r="A133" s="9" t="n"/>
+      <c r="B133" s="9" t="n"/>
+      <c r="C133" s="9" t="n"/>
+      <c r="D133" s="9" t="n"/>
+      <c r="E133" s="9" t="n"/>
+      <c r="F133" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="G133" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H133" s="11" t="inlineStr">
+      <c r="G133" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H133" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama na Berma e berma externa</t>
         </is>
       </c>
-      <c r="I133" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K133" s="9" t="inlineStr"/>
-      <c r="L133" s="9" t="inlineStr"/>
-      <c r="M133" s="8" t="n"/>
+      <c r="I133" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J133" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K133" s="10" t="inlineStr"/>
+      <c r="L133" s="10" t="inlineStr"/>
+      <c r="M133" s="9" t="n"/>
     </row>
     <row r="134" ht="16" customHeight="1">
-      <c r="A134" s="8" t="n"/>
-      <c r="B134" s="8" t="n"/>
-      <c r="C134" s="8" t="n"/>
-      <c r="D134" s="8" t="n"/>
-      <c r="E134" s="8" t="n"/>
+      <c r="A134" s="9" t="n"/>
+      <c r="B134" s="9" t="n"/>
+      <c r="C134" s="9" t="n"/>
+      <c r="D134" s="9" t="n"/>
+      <c r="E134" s="9" t="n"/>
       <c r="F134" s="4" t="n">
         <v>10</v>
       </c>
@@ -5102,45 +5113,45 @@
       <c r="I134" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J134" s="4" t="inlineStr">
+      <c r="J134" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K134" s="4" t="inlineStr"/>
       <c r="L134" s="4" t="inlineStr"/>
-      <c r="M134" s="8" t="n"/>
+      <c r="M134" s="9" t="n"/>
     </row>
     <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="12" t="n"/>
-      <c r="B135" s="12" t="n"/>
-      <c r="C135" s="12" t="n"/>
-      <c r="D135" s="12" t="n"/>
-      <c r="E135" s="12" t="n"/>
-      <c r="F135" s="9" t="n">
+      <c r="A135" s="14" t="n"/>
+      <c r="B135" s="14" t="n"/>
+      <c r="C135" s="14" t="n"/>
+      <c r="D135" s="14" t="n"/>
+      <c r="E135" s="14" t="n"/>
+      <c r="F135" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="G135" s="10" t="inlineStr">
+      <c r="G135" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H135" s="11" t="inlineStr">
+      <c r="H135" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e organização da área</t>
         </is>
       </c>
-      <c r="I135" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J135" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K135" s="9" t="inlineStr"/>
-      <c r="L135" s="9" t="inlineStr"/>
-      <c r="M135" s="12" t="n"/>
+      <c r="I135" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J135" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K135" s="10" t="inlineStr"/>
+      <c r="L135" s="10" t="inlineStr"/>
+      <c r="M135" s="14" t="n"/>
     </row>
     <row r="136" ht="16" customHeight="1">
       <c r="A136" s="4" t="n">
@@ -5180,56 +5191,56 @@
       <c r="I136" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J136" s="4" t="inlineStr">
+      <c r="J136" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr"/>
       <c r="L136" s="4" t="inlineStr"/>
-      <c r="M136" s="4" t="inlineStr">
+      <c r="M136" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="8" t="n"/>
-      <c r="B137" s="8" t="n"/>
-      <c r="C137" s="8" t="n"/>
-      <c r="D137" s="8" t="n"/>
-      <c r="E137" s="8" t="n"/>
-      <c r="F137" s="9" t="n">
+      <c r="A137" s="9" t="n"/>
+      <c r="B137" s="9" t="n"/>
+      <c r="C137" s="9" t="n"/>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G137" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H137" s="11" t="inlineStr">
+      <c r="G137" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H137" s="12" t="inlineStr">
         <is>
           <t>Remoção da grama sobre pontos de subsidência e buracos na Berma</t>
         </is>
       </c>
-      <c r="I137" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J137" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K137" s="9" t="inlineStr"/>
-      <c r="L137" s="9" t="inlineStr"/>
-      <c r="M137" s="8" t="n"/>
+      <c r="I137" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J137" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K137" s="10" t="inlineStr"/>
+      <c r="L137" s="10" t="inlineStr"/>
+      <c r="M137" s="9" t="n"/>
     </row>
     <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="8" t="n"/>
-      <c r="B138" s="8" t="n"/>
-      <c r="C138" s="8" t="n"/>
-      <c r="D138" s="8" t="n"/>
-      <c r="E138" s="8" t="n"/>
+      <c r="A138" s="9" t="n"/>
+      <c r="B138" s="9" t="n"/>
+      <c r="C138" s="9" t="n"/>
+      <c r="D138" s="9" t="n"/>
+      <c r="E138" s="9" t="n"/>
       <c r="F138" s="4" t="n">
         <v>3</v>
       </c>
@@ -5246,52 +5257,52 @@
       <c r="I138" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J138" s="4" t="inlineStr">
+      <c r="J138" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K138" s="4" t="inlineStr"/>
       <c r="L138" s="4" t="inlineStr"/>
-      <c r="M138" s="8" t="n"/>
+      <c r="M138" s="9" t="n"/>
     </row>
     <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="8" t="n"/>
-      <c r="B139" s="8" t="n"/>
-      <c r="C139" s="8" t="n"/>
-      <c r="D139" s="8" t="n"/>
-      <c r="E139" s="8" t="n"/>
-      <c r="F139" s="9" t="n">
+      <c r="A139" s="9" t="n"/>
+      <c r="B139" s="9" t="n"/>
+      <c r="C139" s="9" t="n"/>
+      <c r="D139" s="9" t="n"/>
+      <c r="E139" s="9" t="n"/>
+      <c r="F139" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G139" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr">
+      <c r="G139" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H139" s="12" t="inlineStr">
         <is>
           <t>Compactação do solo nos pontos recompostos</t>
         </is>
       </c>
-      <c r="I139" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J139" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K139" s="9" t="inlineStr"/>
-      <c r="L139" s="9" t="inlineStr"/>
-      <c r="M139" s="8" t="n"/>
+      <c r="I139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K139" s="10" t="inlineStr"/>
+      <c r="L139" s="10" t="inlineStr"/>
+      <c r="M139" s="9" t="n"/>
     </row>
     <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="8" t="n"/>
-      <c r="B140" s="8" t="n"/>
-      <c r="C140" s="8" t="n"/>
-      <c r="D140" s="8" t="n"/>
-      <c r="E140" s="8" t="n"/>
+      <c r="A140" s="9" t="n"/>
+      <c r="B140" s="9" t="n"/>
+      <c r="C140" s="9" t="n"/>
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="9" t="n"/>
       <c r="F140" s="4" t="n">
         <v>5</v>
       </c>
@@ -5308,52 +5319,52 @@
       <c r="I140" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J140" s="4" t="inlineStr">
+      <c r="J140" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr"/>
       <c r="L140" s="4" t="inlineStr"/>
-      <c r="M140" s="8" t="n"/>
+      <c r="M140" s="9" t="n"/>
     </row>
     <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="8" t="n"/>
-      <c r="B141" s="8" t="n"/>
-      <c r="C141" s="8" t="n"/>
-      <c r="D141" s="8" t="n"/>
-      <c r="E141" s="8" t="n"/>
-      <c r="F141" s="9" t="n">
+      <c r="A141" s="9" t="n"/>
+      <c r="B141" s="9" t="n"/>
+      <c r="C141" s="9" t="n"/>
+      <c r="D141" s="9" t="n"/>
+      <c r="E141" s="9" t="n"/>
+      <c r="F141" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G141" s="10" t="inlineStr">
+      <c r="G141" s="11" t="inlineStr">
         <is>
           <t>Macrodrenagem / 5S</t>
         </is>
       </c>
-      <c r="H141" s="11" t="inlineStr">
+      <c r="H141" s="12" t="inlineStr">
         <is>
           <t>Remoção do excedente de terra da berma</t>
         </is>
       </c>
-      <c r="I141" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K141" s="9" t="inlineStr"/>
-      <c r="L141" s="9" t="inlineStr"/>
-      <c r="M141" s="8" t="n"/>
+      <c r="I141" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J141" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K141" s="10" t="inlineStr"/>
+      <c r="L141" s="10" t="inlineStr"/>
+      <c r="M141" s="9" t="n"/>
     </row>
     <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="12" t="n"/>
-      <c r="B142" s="12" t="n"/>
-      <c r="C142" s="12" t="n"/>
-      <c r="D142" s="12" t="n"/>
-      <c r="E142" s="12" t="n"/>
+      <c r="A142" s="14" t="n"/>
+      <c r="B142" s="14" t="n"/>
+      <c r="C142" s="14" t="n"/>
+      <c r="D142" s="14" t="n"/>
+      <c r="E142" s="14" t="n"/>
       <c r="F142" s="4" t="n">
         <v>7</v>
       </c>
@@ -5370,72 +5381,72 @@
       <c r="I142" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J142" s="4" t="inlineStr">
+      <c r="J142" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K142" s="4" t="inlineStr"/>
       <c r="L142" s="4" t="inlineStr"/>
-      <c r="M142" s="12" t="n"/>
+      <c r="M142" s="14" t="n"/>
     </row>
     <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="9" t="n">
+      <c r="A143" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B143" s="13" t="inlineStr">
+      <c r="B143" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C143" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D143" s="13" t="inlineStr">
+      <c r="D143" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="E143" s="9" t="n">
+      <c r="E143" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="F143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G143" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H143" s="11" t="inlineStr">
+      <c r="F143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H143" s="12" t="inlineStr">
         <is>
           <t>Acerto no nivelamento da crista da Berma</t>
         </is>
       </c>
-      <c r="I143" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J143" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K143" s="9" t="inlineStr"/>
-      <c r="L143" s="9" t="inlineStr"/>
-      <c r="M143" s="9" t="inlineStr">
+      <c r="I143" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J143" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K143" s="10" t="inlineStr"/>
+      <c r="L143" s="10" t="inlineStr"/>
+      <c r="M143" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="8" t="n"/>
-      <c r="B144" s="8" t="n"/>
-      <c r="C144" s="8" t="n"/>
-      <c r="D144" s="8" t="n"/>
-      <c r="E144" s="8" t="n"/>
+      <c r="A144" s="9" t="n"/>
+      <c r="B144" s="9" t="n"/>
+      <c r="C144" s="9" t="n"/>
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="9" t="n"/>
       <c r="F144" s="4" t="n">
         <v>2</v>
       </c>
@@ -5452,52 +5463,52 @@
       <c r="I144" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J144" s="4" t="inlineStr">
+      <c r="J144" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr"/>
       <c r="L144" s="4" t="inlineStr"/>
-      <c r="M144" s="8" t="n"/>
+      <c r="M144" s="9" t="n"/>
     </row>
     <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="8" t="n"/>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="8" t="n"/>
-      <c r="D145" s="8" t="n"/>
-      <c r="E145" s="8" t="n"/>
-      <c r="F145" s="9" t="n">
+      <c r="A145" s="9" t="n"/>
+      <c r="B145" s="9" t="n"/>
+      <c r="C145" s="9" t="n"/>
+      <c r="D145" s="9" t="n"/>
+      <c r="E145" s="9" t="n"/>
+      <c r="F145" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G145" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H145" s="11" t="inlineStr">
+      <c r="G145" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e nivelamento nos pontos de buraco/cavidade</t>
         </is>
       </c>
-      <c r="I145" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J145" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K145" s="9" t="inlineStr"/>
-      <c r="L145" s="9" t="inlineStr"/>
-      <c r="M145" s="8" t="n"/>
+      <c r="I145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K145" s="10" t="inlineStr"/>
+      <c r="L145" s="10" t="inlineStr"/>
+      <c r="M145" s="9" t="n"/>
     </row>
     <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="8" t="n"/>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="8" t="n"/>
+      <c r="A146" s="9" t="n"/>
+      <c r="B146" s="9" t="n"/>
+      <c r="C146" s="9" t="n"/>
+      <c r="D146" s="9" t="n"/>
+      <c r="E146" s="9" t="n"/>
       <c r="F146" s="4" t="n">
         <v>4</v>
       </c>
@@ -5514,52 +5525,52 @@
       <c r="I146" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J146" s="4" t="inlineStr">
+      <c r="J146" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K146" s="4" t="inlineStr"/>
       <c r="L146" s="4" t="inlineStr"/>
-      <c r="M146" s="8" t="n"/>
+      <c r="M146" s="9" t="n"/>
     </row>
     <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="8" t="n"/>
-      <c r="B147" s="8" t="n"/>
-      <c r="C147" s="8" t="n"/>
-      <c r="D147" s="8" t="n"/>
-      <c r="E147" s="8" t="n"/>
-      <c r="F147" s="9" t="n">
+      <c r="A147" s="9" t="n"/>
+      <c r="B147" s="9" t="n"/>
+      <c r="C147" s="9" t="n"/>
+      <c r="D147" s="9" t="n"/>
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G147" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H147" s="11" t="inlineStr">
+      <c r="G147" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama na Berma e berma externa</t>
         </is>
       </c>
-      <c r="I147" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J147" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr"/>
-      <c r="L147" s="9" t="inlineStr"/>
-      <c r="M147" s="8" t="n"/>
+      <c r="I147" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J147" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K147" s="10" t="inlineStr"/>
+      <c r="L147" s="10" t="inlineStr"/>
+      <c r="M147" s="9" t="n"/>
     </row>
     <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="8" t="n"/>
-      <c r="B148" s="8" t="n"/>
-      <c r="C148" s="8" t="n"/>
-      <c r="D148" s="8" t="n"/>
-      <c r="E148" s="8" t="n"/>
+      <c r="A148" s="9" t="n"/>
+      <c r="B148" s="9" t="n"/>
+      <c r="C148" s="9" t="n"/>
+      <c r="D148" s="9" t="n"/>
+      <c r="E148" s="9" t="n"/>
       <c r="F148" s="4" t="n">
         <v>6</v>
       </c>
@@ -5576,45 +5587,45 @@
       <c r="I148" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J148" s="4" t="inlineStr">
+      <c r="J148" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K148" s="4" t="inlineStr"/>
       <c r="L148" s="4" t="inlineStr"/>
-      <c r="M148" s="8" t="n"/>
+      <c r="M148" s="9" t="n"/>
     </row>
     <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="12" t="n"/>
-      <c r="B149" s="12" t="n"/>
-      <c r="C149" s="12" t="n"/>
-      <c r="D149" s="12" t="n"/>
-      <c r="E149" s="12" t="n"/>
-      <c r="F149" s="9" t="n">
+      <c r="A149" s="14" t="n"/>
+      <c r="B149" s="14" t="n"/>
+      <c r="C149" s="14" t="n"/>
+      <c r="D149" s="14" t="n"/>
+      <c r="E149" s="14" t="n"/>
+      <c r="F149" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G149" s="10" t="inlineStr">
+      <c r="G149" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H149" s="11" t="inlineStr">
+      <c r="H149" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e organização da área</t>
         </is>
       </c>
-      <c r="I149" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J149" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K149" s="9" t="inlineStr"/>
-      <c r="L149" s="9" t="inlineStr"/>
-      <c r="M149" s="12" t="n"/>
+      <c r="I149" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J149" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K149" s="10" t="inlineStr"/>
+      <c r="L149" s="10" t="inlineStr"/>
+      <c r="M149" s="14" t="n"/>
     </row>
     <row r="150" ht="16" customHeight="1">
       <c r="A150" s="4" t="n">
@@ -5654,56 +5665,56 @@
       <c r="I150" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J150" s="4" t="inlineStr">
+      <c r="J150" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr"/>
       <c r="L150" s="4" t="inlineStr"/>
-      <c r="M150" s="4" t="inlineStr">
+      <c r="M150" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="8" t="n"/>
-      <c r="B151" s="8" t="n"/>
-      <c r="C151" s="8" t="n"/>
-      <c r="D151" s="8" t="n"/>
-      <c r="E151" s="8" t="n"/>
-      <c r="F151" s="9" t="n">
+      <c r="A151" s="9" t="n"/>
+      <c r="B151" s="9" t="n"/>
+      <c r="C151" s="9" t="n"/>
+      <c r="D151" s="9" t="n"/>
+      <c r="E151" s="9" t="n"/>
+      <c r="F151" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G151" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H151" s="11" t="inlineStr">
+      <c r="G151" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H151" s="12" t="inlineStr">
         <is>
           <t>Remoção da grama sobre pontos de subsidência e buracos na Berma</t>
         </is>
       </c>
-      <c r="I151" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J151" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K151" s="9" t="inlineStr"/>
-      <c r="L151" s="9" t="inlineStr"/>
-      <c r="M151" s="8" t="n"/>
+      <c r="I151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J151" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K151" s="10" t="inlineStr"/>
+      <c r="L151" s="10" t="inlineStr"/>
+      <c r="M151" s="9" t="n"/>
     </row>
     <row r="152" ht="16" customHeight="1">
-      <c r="A152" s="8" t="n"/>
-      <c r="B152" s="8" t="n"/>
-      <c r="C152" s="8" t="n"/>
-      <c r="D152" s="8" t="n"/>
-      <c r="E152" s="8" t="n"/>
+      <c r="A152" s="9" t="n"/>
+      <c r="B152" s="9" t="n"/>
+      <c r="C152" s="9" t="n"/>
+      <c r="D152" s="9" t="n"/>
+      <c r="E152" s="9" t="n"/>
       <c r="F152" s="4" t="n">
         <v>3</v>
       </c>
@@ -5720,52 +5731,52 @@
       <c r="I152" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J152" s="4" t="inlineStr">
+      <c r="J152" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K152" s="4" t="inlineStr"/>
       <c r="L152" s="4" t="inlineStr"/>
-      <c r="M152" s="8" t="n"/>
+      <c r="M152" s="9" t="n"/>
     </row>
     <row r="153" ht="16" customHeight="1">
-      <c r="A153" s="8" t="n"/>
-      <c r="B153" s="8" t="n"/>
-      <c r="C153" s="8" t="n"/>
-      <c r="D153" s="8" t="n"/>
-      <c r="E153" s="8" t="n"/>
-      <c r="F153" s="9" t="n">
+      <c r="A153" s="9" t="n"/>
+      <c r="B153" s="9" t="n"/>
+      <c r="C153" s="9" t="n"/>
+      <c r="D153" s="9" t="n"/>
+      <c r="E153" s="9" t="n"/>
+      <c r="F153" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G153" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H153" s="11" t="inlineStr">
+      <c r="G153" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H153" s="12" t="inlineStr">
         <is>
           <t>Compactação do solo nos pontos recompostos</t>
         </is>
       </c>
-      <c r="I153" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K153" s="9" t="inlineStr"/>
-      <c r="L153" s="9" t="inlineStr"/>
-      <c r="M153" s="8" t="n"/>
+      <c r="I153" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J153" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K153" s="10" t="inlineStr"/>
+      <c r="L153" s="10" t="inlineStr"/>
+      <c r="M153" s="9" t="n"/>
     </row>
     <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="8" t="n"/>
-      <c r="B154" s="8" t="n"/>
-      <c r="C154" s="8" t="n"/>
-      <c r="D154" s="8" t="n"/>
-      <c r="E154" s="8" t="n"/>
+      <c r="A154" s="9" t="n"/>
+      <c r="B154" s="9" t="n"/>
+      <c r="C154" s="9" t="n"/>
+      <c r="D154" s="9" t="n"/>
+      <c r="E154" s="9" t="n"/>
       <c r="F154" s="4" t="n">
         <v>5</v>
       </c>
@@ -5782,52 +5793,52 @@
       <c r="I154" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J154" s="4" t="inlineStr">
+      <c r="J154" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K154" s="4" t="inlineStr"/>
       <c r="L154" s="4" t="inlineStr"/>
-      <c r="M154" s="8" t="n"/>
+      <c r="M154" s="9" t="n"/>
     </row>
     <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="8" t="n"/>
-      <c r="B155" s="8" t="n"/>
-      <c r="C155" s="8" t="n"/>
-      <c r="D155" s="8" t="n"/>
-      <c r="E155" s="8" t="n"/>
-      <c r="F155" s="9" t="n">
+      <c r="A155" s="9" t="n"/>
+      <c r="B155" s="9" t="n"/>
+      <c r="C155" s="9" t="n"/>
+      <c r="D155" s="9" t="n"/>
+      <c r="E155" s="9" t="n"/>
+      <c r="F155" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G155" s="10" t="inlineStr">
+      <c r="G155" s="11" t="inlineStr">
         <is>
           <t>Macrodrenagem / 5S</t>
         </is>
       </c>
-      <c r="H155" s="11" t="inlineStr">
+      <c r="H155" s="12" t="inlineStr">
         <is>
           <t>Remoção do excedente de terra da berma</t>
         </is>
       </c>
-      <c r="I155" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J155" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K155" s="9" t="inlineStr"/>
-      <c r="L155" s="9" t="inlineStr"/>
-      <c r="M155" s="8" t="n"/>
+      <c r="I155" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J155" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K155" s="10" t="inlineStr"/>
+      <c r="L155" s="10" t="inlineStr"/>
+      <c r="M155" s="9" t="n"/>
     </row>
     <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="12" t="n"/>
-      <c r="B156" s="12" t="n"/>
-      <c r="C156" s="12" t="n"/>
-      <c r="D156" s="12" t="n"/>
-      <c r="E156" s="12" t="n"/>
+      <c r="A156" s="14" t="n"/>
+      <c r="B156" s="14" t="n"/>
+      <c r="C156" s="14" t="n"/>
+      <c r="D156" s="14" t="n"/>
+      <c r="E156" s="14" t="n"/>
       <c r="F156" s="4" t="n">
         <v>7</v>
       </c>
@@ -5844,72 +5855,72 @@
       <c r="I156" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J156" s="4" t="inlineStr">
+      <c r="J156" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K156" s="4" t="inlineStr"/>
       <c r="L156" s="4" t="inlineStr"/>
-      <c r="M156" s="12" t="n"/>
+      <c r="M156" s="14" t="n"/>
     </row>
     <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="9" t="n">
+      <c r="A157" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="B157" s="13" t="inlineStr">
+      <c r="B157" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="C157" s="9" t="inlineStr">
+      <c r="C157" s="10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D157" s="13" t="inlineStr">
+      <c r="D157" s="15" t="inlineStr">
         <is>
           <t>Berma Externa — Acompanhamento da Rua</t>
         </is>
       </c>
-      <c r="E157" s="9" t="n">
+      <c r="E157" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="F157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G157" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H157" s="11" t="inlineStr">
+      <c r="F157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G157" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="inlineStr">
         <is>
           <t>Reaterro na face lateral da canaleta de 50cm</t>
         </is>
       </c>
-      <c r="I157" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K157" s="9" t="inlineStr"/>
-      <c r="L157" s="9" t="inlineStr"/>
-      <c r="M157" s="9" t="inlineStr">
+      <c r="I157" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J157" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K157" s="10" t="inlineStr"/>
+      <c r="L157" s="10" t="inlineStr"/>
+      <c r="M157" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="8" t="n"/>
-      <c r="B158" s="8" t="n"/>
-      <c r="C158" s="8" t="n"/>
-      <c r="D158" s="8" t="n"/>
-      <c r="E158" s="8" t="n"/>
+      <c r="A158" s="9" t="n"/>
+      <c r="B158" s="9" t="n"/>
+      <c r="C158" s="9" t="n"/>
+      <c r="D158" s="9" t="n"/>
+      <c r="E158" s="9" t="n"/>
       <c r="F158" s="4" t="n">
         <v>2</v>
       </c>
@@ -5926,52 +5937,52 @@
       <c r="I158" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J158" s="4" t="inlineStr">
+      <c r="J158" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr"/>
       <c r="L158" s="4" t="inlineStr"/>
-      <c r="M158" s="8" t="n"/>
+      <c r="M158" s="9" t="n"/>
     </row>
     <row r="159" ht="16" customHeight="1">
-      <c r="A159" s="8" t="n"/>
-      <c r="B159" s="8" t="n"/>
-      <c r="C159" s="8" t="n"/>
-      <c r="D159" s="8" t="n"/>
-      <c r="E159" s="8" t="n"/>
-      <c r="F159" s="9" t="n">
+      <c r="A159" s="9" t="n"/>
+      <c r="B159" s="9" t="n"/>
+      <c r="C159" s="9" t="n"/>
+      <c r="D159" s="9" t="n"/>
+      <c r="E159" s="9" t="n"/>
+      <c r="F159" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G159" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H159" s="11" t="inlineStr">
+      <c r="G159" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H159" s="12" t="inlineStr">
         <is>
           <t>Limpeza interna da canaleta (remoção de sedimento acumulado)</t>
         </is>
       </c>
-      <c r="I159" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J159" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K159" s="9" t="inlineStr"/>
-      <c r="L159" s="9" t="inlineStr"/>
-      <c r="M159" s="8" t="n"/>
+      <c r="I159" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K159" s="10" t="inlineStr"/>
+      <c r="L159" s="10" t="inlineStr"/>
+      <c r="M159" s="9" t="n"/>
     </row>
     <row r="160" ht="16" customHeight="1">
-      <c r="A160" s="8" t="n"/>
-      <c r="B160" s="8" t="n"/>
-      <c r="C160" s="8" t="n"/>
-      <c r="D160" s="8" t="n"/>
-      <c r="E160" s="8" t="n"/>
+      <c r="A160" s="9" t="n"/>
+      <c r="B160" s="9" t="n"/>
+      <c r="C160" s="9" t="n"/>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="9" t="n"/>
       <c r="F160" s="4" t="n">
         <v>4</v>
       </c>
@@ -5988,52 +5999,52 @@
       <c r="I160" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J160" s="4" t="inlineStr">
+      <c r="J160" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr"/>
       <c r="L160" s="4" t="inlineStr"/>
-      <c r="M160" s="8" t="n"/>
+      <c r="M160" s="9" t="n"/>
     </row>
     <row r="161" ht="16" customHeight="1">
-      <c r="A161" s="8" t="n"/>
-      <c r="B161" s="8" t="n"/>
-      <c r="C161" s="8" t="n"/>
-      <c r="D161" s="8" t="n"/>
-      <c r="E161" s="8" t="n"/>
-      <c r="F161" s="9" t="n">
+      <c r="A161" s="9" t="n"/>
+      <c r="B161" s="9" t="n"/>
+      <c r="C161" s="9" t="n"/>
+      <c r="D161" s="9" t="n"/>
+      <c r="E161" s="9" t="n"/>
+      <c r="F161" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G161" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H161" s="11" t="inlineStr">
+      <c r="G161" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H161" s="12" t="inlineStr">
         <is>
           <t>Acerto no nivelamento da crista da Berma</t>
         </is>
       </c>
-      <c r="I161" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J161" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K161" s="9" t="inlineStr"/>
-      <c r="L161" s="9" t="inlineStr"/>
-      <c r="M161" s="8" t="n"/>
+      <c r="I161" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J161" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K161" s="10" t="inlineStr"/>
+      <c r="L161" s="10" t="inlineStr"/>
+      <c r="M161" s="9" t="n"/>
     </row>
     <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="8" t="n"/>
-      <c r="B162" s="8" t="n"/>
-      <c r="C162" s="8" t="n"/>
-      <c r="D162" s="8" t="n"/>
-      <c r="E162" s="8" t="n"/>
+      <c r="A162" s="9" t="n"/>
+      <c r="B162" s="9" t="n"/>
+      <c r="C162" s="9" t="n"/>
+      <c r="D162" s="9" t="n"/>
+      <c r="E162" s="9" t="n"/>
       <c r="F162" s="4" t="n">
         <v>6</v>
       </c>
@@ -6050,52 +6061,52 @@
       <c r="I162" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J162" s="4" t="inlineStr">
+      <c r="J162" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K162" s="4" t="inlineStr"/>
       <c r="L162" s="4" t="inlineStr"/>
-      <c r="M162" s="8" t="n"/>
+      <c r="M162" s="9" t="n"/>
     </row>
     <row r="163" ht="16" customHeight="1">
-      <c r="A163" s="8" t="n"/>
-      <c r="B163" s="8" t="n"/>
-      <c r="C163" s="8" t="n"/>
-      <c r="D163" s="8" t="n"/>
-      <c r="E163" s="8" t="n"/>
-      <c r="F163" s="9" t="n">
+      <c r="A163" s="9" t="n"/>
+      <c r="B163" s="9" t="n"/>
+      <c r="C163" s="9" t="n"/>
+      <c r="D163" s="9" t="n"/>
+      <c r="E163" s="9" t="n"/>
+      <c r="F163" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="G163" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H163" s="11" t="inlineStr">
+      <c r="G163" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H163" s="12" t="inlineStr">
         <is>
           <t>Recomposição do solo e nivelamento nos pontos de buraco/cavidade</t>
         </is>
       </c>
-      <c r="I163" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J163" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K163" s="9" t="inlineStr"/>
-      <c r="L163" s="9" t="inlineStr"/>
-      <c r="M163" s="8" t="n"/>
+      <c r="I163" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J163" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K163" s="10" t="inlineStr"/>
+      <c r="L163" s="10" t="inlineStr"/>
+      <c r="M163" s="9" t="n"/>
     </row>
     <row r="164" ht="16" customHeight="1">
-      <c r="A164" s="8" t="n"/>
-      <c r="B164" s="8" t="n"/>
-      <c r="C164" s="8" t="n"/>
-      <c r="D164" s="8" t="n"/>
-      <c r="E164" s="8" t="n"/>
+      <c r="A164" s="9" t="n"/>
+      <c r="B164" s="9" t="n"/>
+      <c r="C164" s="9" t="n"/>
+      <c r="D164" s="9" t="n"/>
+      <c r="E164" s="9" t="n"/>
       <c r="F164" s="4" t="n">
         <v>8</v>
       </c>
@@ -6112,52 +6123,52 @@
       <c r="I164" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J164" s="4" t="inlineStr">
+      <c r="J164" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K164" s="4" t="inlineStr"/>
       <c r="L164" s="4" t="inlineStr"/>
-      <c r="M164" s="8" t="n"/>
+      <c r="M164" s="9" t="n"/>
     </row>
     <row r="165" ht="16" customHeight="1">
-      <c r="A165" s="8" t="n"/>
-      <c r="B165" s="8" t="n"/>
-      <c r="C165" s="8" t="n"/>
-      <c r="D165" s="8" t="n"/>
-      <c r="E165" s="8" t="n"/>
-      <c r="F165" s="9" t="n">
+      <c r="A165" s="9" t="n"/>
+      <c r="B165" s="9" t="n"/>
+      <c r="C165" s="9" t="n"/>
+      <c r="D165" s="9" t="n"/>
+      <c r="E165" s="9" t="n"/>
+      <c r="F165" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="G165" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H165" s="11" t="inlineStr">
+      <c r="G165" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H165" s="12" t="inlineStr">
         <is>
           <t>Replantio de grama na Berma e berma externa</t>
         </is>
       </c>
-      <c r="I165" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K165" s="9" t="inlineStr"/>
-      <c r="L165" s="9" t="inlineStr"/>
-      <c r="M165" s="8" t="n"/>
+      <c r="I165" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J165" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K165" s="10" t="inlineStr"/>
+      <c r="L165" s="10" t="inlineStr"/>
+      <c r="M165" s="9" t="n"/>
     </row>
     <row r="166" ht="16" customHeight="1">
-      <c r="A166" s="8" t="n"/>
-      <c r="B166" s="8" t="n"/>
-      <c r="C166" s="8" t="n"/>
-      <c r="D166" s="8" t="n"/>
-      <c r="E166" s="8" t="n"/>
+      <c r="A166" s="9" t="n"/>
+      <c r="B166" s="9" t="n"/>
+      <c r="C166" s="9" t="n"/>
+      <c r="D166" s="9" t="n"/>
+      <c r="E166" s="9" t="n"/>
       <c r="F166" s="4" t="n">
         <v>10</v>
       </c>
@@ -6174,45 +6185,45 @@
       <c r="I166" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J166" s="4" t="inlineStr">
+      <c r="J166" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K166" s="4" t="inlineStr"/>
       <c r="L166" s="4" t="inlineStr"/>
-      <c r="M166" s="8" t="n"/>
+      <c r="M166" s="9" t="n"/>
     </row>
     <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="12" t="n"/>
-      <c r="B167" s="12" t="n"/>
-      <c r="C167" s="12" t="n"/>
-      <c r="D167" s="12" t="n"/>
-      <c r="E167" s="12" t="n"/>
-      <c r="F167" s="9" t="n">
+      <c r="A167" s="14" t="n"/>
+      <c r="B167" s="14" t="n"/>
+      <c r="C167" s="14" t="n"/>
+      <c r="D167" s="14" t="n"/>
+      <c r="E167" s="14" t="n"/>
+      <c r="F167" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="G167" s="10" t="inlineStr">
+      <c r="G167" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H167" s="11" t="inlineStr">
+      <c r="H167" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e organização da área</t>
         </is>
       </c>
-      <c r="I167" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J167" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K167" s="9" t="inlineStr"/>
-      <c r="L167" s="9" t="inlineStr"/>
-      <c r="M167" s="12" t="n"/>
+      <c r="I167" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J167" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K167" s="10" t="inlineStr"/>
+      <c r="L167" s="10" t="inlineStr"/>
+      <c r="M167" s="14" t="n"/>
     </row>
     <row r="168" ht="16" customHeight="1">
       <c r="A168" s="4" t="n">
@@ -6252,56 +6263,56 @@
       <c r="I168" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J168" s="4" t="inlineStr">
+      <c r="J168" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K168" s="4" t="inlineStr"/>
       <c r="L168" s="4" t="inlineStr"/>
-      <c r="M168" s="4" t="inlineStr">
+      <c r="M168" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="169" ht="16" customHeight="1">
-      <c r="A169" s="8" t="n"/>
-      <c r="B169" s="8" t="n"/>
-      <c r="C169" s="8" t="n"/>
-      <c r="D169" s="8" t="n"/>
-      <c r="E169" s="8" t="n"/>
-      <c r="F169" s="9" t="n">
+      <c r="A169" s="9" t="n"/>
+      <c r="B169" s="9" t="n"/>
+      <c r="C169" s="9" t="n"/>
+      <c r="D169" s="9" t="n"/>
+      <c r="E169" s="9" t="n"/>
+      <c r="F169" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G169" s="10" t="inlineStr">
+      <c r="G169" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H169" s="11" t="inlineStr">
+      <c r="H169" s="12" t="inlineStr">
         <is>
           <t>Nivelamento do solo</t>
         </is>
       </c>
-      <c r="I169" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J169" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K169" s="9" t="inlineStr"/>
-      <c r="L169" s="9" t="inlineStr"/>
-      <c r="M169" s="8" t="n"/>
+      <c r="I169" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J169" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K169" s="10" t="inlineStr"/>
+      <c r="L169" s="10" t="inlineStr"/>
+      <c r="M169" s="9" t="n"/>
     </row>
     <row r="170" ht="16" customHeight="1">
-      <c r="A170" s="8" t="n"/>
-      <c r="B170" s="8" t="n"/>
-      <c r="C170" s="8" t="n"/>
-      <c r="D170" s="8" t="n"/>
-      <c r="E170" s="8" t="n"/>
+      <c r="A170" s="9" t="n"/>
+      <c r="B170" s="9" t="n"/>
+      <c r="C170" s="9" t="n"/>
+      <c r="D170" s="9" t="n"/>
+      <c r="E170" s="9" t="n"/>
       <c r="F170" s="4" t="n">
         <v>3</v>
       </c>
@@ -6318,52 +6329,52 @@
       <c r="I170" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J170" s="4" t="inlineStr">
+      <c r="J170" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K170" s="4" t="inlineStr"/>
       <c r="L170" s="4" t="inlineStr"/>
-      <c r="M170" s="8" t="n"/>
+      <c r="M170" s="9" t="n"/>
     </row>
     <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="8" t="n"/>
-      <c r="B171" s="8" t="n"/>
-      <c r="C171" s="8" t="n"/>
-      <c r="D171" s="8" t="n"/>
-      <c r="E171" s="8" t="n"/>
-      <c r="F171" s="9" t="n">
+      <c r="A171" s="9" t="n"/>
+      <c r="B171" s="9" t="n"/>
+      <c r="C171" s="9" t="n"/>
+      <c r="D171" s="9" t="n"/>
+      <c r="E171" s="9" t="n"/>
+      <c r="F171" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="G171" s="10" t="inlineStr">
+      <c r="G171" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H171" s="11" t="inlineStr">
+      <c r="H171" s="12" t="inlineStr">
         <is>
           <t>Plantio de grama</t>
         </is>
       </c>
-      <c r="I171" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J171" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K171" s="9" t="inlineStr"/>
-      <c r="L171" s="9" t="inlineStr"/>
-      <c r="M171" s="8" t="n"/>
+      <c r="I171" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J171" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K171" s="10" t="inlineStr"/>
+      <c r="L171" s="10" t="inlineStr"/>
+      <c r="M171" s="9" t="n"/>
     </row>
     <row r="172" ht="16" customHeight="1">
-      <c r="A172" s="8" t="n"/>
-      <c r="B172" s="8" t="n"/>
-      <c r="C172" s="8" t="n"/>
-      <c r="D172" s="8" t="n"/>
-      <c r="E172" s="8" t="n"/>
+      <c r="A172" s="9" t="n"/>
+      <c r="B172" s="9" t="n"/>
+      <c r="C172" s="9" t="n"/>
+      <c r="D172" s="9" t="n"/>
+      <c r="E172" s="9" t="n"/>
       <c r="F172" s="4" t="n">
         <v>5</v>
       </c>
@@ -6380,45 +6391,45 @@
       <c r="I172" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J172" s="4" t="inlineStr">
+      <c r="J172" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr"/>
       <c r="L172" s="4" t="inlineStr"/>
-      <c r="M172" s="8" t="n"/>
+      <c r="M172" s="9" t="n"/>
     </row>
     <row r="173" ht="16" customHeight="1">
-      <c r="A173" s="12" t="n"/>
-      <c r="B173" s="12" t="n"/>
-      <c r="C173" s="12" t="n"/>
-      <c r="D173" s="12" t="n"/>
-      <c r="E173" s="12" t="n"/>
-      <c r="F173" s="9" t="n">
+      <c r="A173" s="14" t="n"/>
+      <c r="B173" s="14" t="n"/>
+      <c r="C173" s="14" t="n"/>
+      <c r="D173" s="14" t="n"/>
+      <c r="E173" s="14" t="n"/>
+      <c r="F173" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="G173" s="10" t="inlineStr">
+      <c r="G173" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H173" s="11" t="inlineStr">
+      <c r="H173" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I173" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J173" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K173" s="9" t="inlineStr"/>
-      <c r="L173" s="9" t="inlineStr"/>
-      <c r="M173" s="12" t="n"/>
+      <c r="I173" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J173" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K173" s="10" t="inlineStr"/>
+      <c r="L173" s="10" t="inlineStr"/>
+      <c r="M173" s="14" t="n"/>
     </row>
     <row r="174" ht="16" customHeight="1">
       <c r="A174" s="4" t="n">
@@ -6458,56 +6469,56 @@
       <c r="I174" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J174" s="4" t="inlineStr">
+      <c r="J174" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr"/>
       <c r="L174" s="4" t="inlineStr"/>
-      <c r="M174" s="4" t="inlineStr">
+      <c r="M174" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="8" t="n"/>
-      <c r="B175" s="8" t="n"/>
-      <c r="C175" s="8" t="n"/>
-      <c r="D175" s="8" t="n"/>
-      <c r="E175" s="8" t="n"/>
-      <c r="F175" s="9" t="n">
+      <c r="A175" s="9" t="n"/>
+      <c r="B175" s="9" t="n"/>
+      <c r="C175" s="9" t="n"/>
+      <c r="D175" s="9" t="n"/>
+      <c r="E175" s="9" t="n"/>
+      <c r="F175" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G175" s="10" t="inlineStr">
+      <c r="G175" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H175" s="11" t="inlineStr">
+      <c r="H175" s="12" t="inlineStr">
         <is>
           <t>Nivelamento superficial da superfície</t>
         </is>
       </c>
-      <c r="I175" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J175" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K175" s="9" t="inlineStr"/>
-      <c r="L175" s="9" t="inlineStr"/>
-      <c r="M175" s="8" t="n"/>
+      <c r="I175" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J175" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K175" s="10" t="inlineStr"/>
+      <c r="L175" s="10" t="inlineStr"/>
+      <c r="M175" s="9" t="n"/>
     </row>
     <row r="176" ht="16" customHeight="1">
-      <c r="A176" s="12" t="n"/>
-      <c r="B176" s="12" t="n"/>
-      <c r="C176" s="12" t="n"/>
-      <c r="D176" s="12" t="n"/>
-      <c r="E176" s="12" t="n"/>
+      <c r="A176" s="14" t="n"/>
+      <c r="B176" s="14" t="n"/>
+      <c r="C176" s="14" t="n"/>
+      <c r="D176" s="14" t="n"/>
+      <c r="E176" s="14" t="n"/>
       <c r="F176" s="4" t="n">
         <v>3</v>
       </c>
@@ -6524,72 +6535,72 @@
       <c r="I176" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J176" s="4" t="inlineStr">
+      <c r="J176" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr"/>
       <c r="L176" s="4" t="inlineStr"/>
-      <c r="M176" s="12" t="n"/>
+      <c r="M176" s="14" t="n"/>
     </row>
     <row r="177" ht="16" customHeight="1">
-      <c r="A177" s="9" t="n">
+      <c r="A177" s="10" t="n">
         <v>27</v>
       </c>
-      <c r="B177" s="13" t="inlineStr">
+      <c r="B177" s="15" t="inlineStr">
         <is>
           <t>Platô — Área de Tancagem</t>
         </is>
       </c>
-      <c r="C177" s="9" t="inlineStr">
+      <c r="C177" s="10" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D177" s="13" t="inlineStr">
+      <c r="D177" s="15" t="inlineStr">
         <is>
           <t>Platô — Área de Tancagem</t>
         </is>
       </c>
-      <c r="E177" s="9" t="n">
+      <c r="E177" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F177" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G177" s="10" t="inlineStr">
+      <c r="F177" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G177" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H177" s="11" t="inlineStr">
+      <c r="H177" s="12" t="inlineStr">
         <is>
           <t>Aplicação de água com caminhão pipa</t>
         </is>
       </c>
-      <c r="I177" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J177" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K177" s="9" t="inlineStr"/>
-      <c r="L177" s="9" t="inlineStr"/>
-      <c r="M177" s="9" t="inlineStr">
+      <c r="I177" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J177" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K177" s="10" t="inlineStr"/>
+      <c r="L177" s="10" t="inlineStr"/>
+      <c r="M177" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="178" ht="16" customHeight="1">
-      <c r="A178" s="8" t="n"/>
-      <c r="B178" s="8" t="n"/>
-      <c r="C178" s="8" t="n"/>
-      <c r="D178" s="8" t="n"/>
-      <c r="E178" s="8" t="n"/>
+      <c r="A178" s="9" t="n"/>
+      <c r="B178" s="9" t="n"/>
+      <c r="C178" s="9" t="n"/>
+      <c r="D178" s="9" t="n"/>
+      <c r="E178" s="9" t="n"/>
       <c r="F178" s="4" t="n">
         <v>2</v>
       </c>
@@ -6606,45 +6617,45 @@
       <c r="I178" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J178" s="4" t="inlineStr">
+      <c r="J178" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K178" s="4" t="inlineStr"/>
       <c r="L178" s="4" t="inlineStr"/>
-      <c r="M178" s="8" t="n"/>
+      <c r="M178" s="9" t="n"/>
     </row>
     <row r="179" ht="16" customHeight="1">
-      <c r="A179" s="12" t="n"/>
-      <c r="B179" s="12" t="n"/>
-      <c r="C179" s="12" t="n"/>
-      <c r="D179" s="12" t="n"/>
-      <c r="E179" s="12" t="n"/>
-      <c r="F179" s="9" t="n">
+      <c r="A179" s="14" t="n"/>
+      <c r="B179" s="14" t="n"/>
+      <c r="C179" s="14" t="n"/>
+      <c r="D179" s="14" t="n"/>
+      <c r="E179" s="14" t="n"/>
+      <c r="F179" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G179" s="10" t="inlineStr">
+      <c r="G179" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H179" s="11" t="inlineStr">
+      <c r="H179" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I179" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J179" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K179" s="9" t="inlineStr"/>
-      <c r="L179" s="9" t="inlineStr"/>
-      <c r="M179" s="12" t="n"/>
+      <c r="I179" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K179" s="10" t="inlineStr"/>
+      <c r="L179" s="10" t="inlineStr"/>
+      <c r="M179" s="14" t="n"/>
     </row>
     <row r="180" ht="16" customHeight="1">
       <c r="A180" s="4" t="n">
@@ -6684,56 +6695,56 @@
       <c r="I180" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J180" s="4" t="inlineStr">
+      <c r="J180" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr"/>
       <c r="L180" s="4" t="inlineStr"/>
-      <c r="M180" s="4" t="inlineStr">
+      <c r="M180" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="181" ht="16" customHeight="1">
-      <c r="A181" s="8" t="n"/>
-      <c r="B181" s="8" t="n"/>
-      <c r="C181" s="8" t="n"/>
-      <c r="D181" s="8" t="n"/>
-      <c r="E181" s="8" t="n"/>
-      <c r="F181" s="9" t="n">
+      <c r="A181" s="9" t="n"/>
+      <c r="B181" s="9" t="n"/>
+      <c r="C181" s="9" t="n"/>
+      <c r="D181" s="9" t="n"/>
+      <c r="E181" s="9" t="n"/>
+      <c r="F181" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G181" s="10" t="inlineStr">
+      <c r="G181" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H181" s="11" t="inlineStr">
+      <c r="H181" s="12" t="inlineStr">
         <is>
           <t>Nivelamento superficial da superfície</t>
         </is>
       </c>
-      <c r="I181" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J181" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K181" s="9" t="inlineStr"/>
-      <c r="L181" s="9" t="inlineStr"/>
-      <c r="M181" s="8" t="n"/>
+      <c r="I181" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K181" s="10" t="inlineStr"/>
+      <c r="L181" s="10" t="inlineStr"/>
+      <c r="M181" s="9" t="n"/>
     </row>
     <row r="182" ht="16" customHeight="1">
-      <c r="A182" s="12" t="n"/>
-      <c r="B182" s="12" t="n"/>
-      <c r="C182" s="12" t="n"/>
-      <c r="D182" s="12" t="n"/>
-      <c r="E182" s="12" t="n"/>
+      <c r="A182" s="14" t="n"/>
+      <c r="B182" s="14" t="n"/>
+      <c r="C182" s="14" t="n"/>
+      <c r="D182" s="14" t="n"/>
+      <c r="E182" s="14" t="n"/>
       <c r="F182" s="4" t="n">
         <v>3</v>
       </c>
@@ -6750,72 +6761,72 @@
       <c r="I182" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J182" s="4" t="inlineStr">
+      <c r="J182" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K182" s="4" t="inlineStr"/>
       <c r="L182" s="4" t="inlineStr"/>
-      <c r="M182" s="12" t="n"/>
+      <c r="M182" s="14" t="n"/>
     </row>
     <row r="183" ht="16" customHeight="1">
-      <c r="A183" s="9" t="n">
+      <c r="A183" s="10" t="n">
         <v>29</v>
       </c>
-      <c r="B183" s="13" t="inlineStr">
+      <c r="B183" s="15" t="inlineStr">
         <is>
           <t>Talude do Fundo da Obra</t>
         </is>
       </c>
-      <c r="C183" s="9" t="inlineStr">
+      <c r="C183" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D183" s="13" t="inlineStr">
+      <c r="D183" s="15" t="inlineStr">
         <is>
           <t>Talude do Fundo da Obra</t>
         </is>
       </c>
-      <c r="E183" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F183" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G183" s="10" t="inlineStr">
+      <c r="E183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G183" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H183" s="11" t="inlineStr">
+      <c r="H183" s="12" t="inlineStr">
         <is>
           <t>Realinhamento da grama</t>
         </is>
       </c>
-      <c r="I183" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J183" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K183" s="9" t="inlineStr"/>
-      <c r="L183" s="9" t="inlineStr"/>
-      <c r="M183" s="9" t="inlineStr">
+      <c r="I183" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J183" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K183" s="10" t="inlineStr"/>
+      <c r="L183" s="10" t="inlineStr"/>
+      <c r="M183" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="184" ht="16" customHeight="1">
-      <c r="A184" s="8" t="n"/>
-      <c r="B184" s="8" t="n"/>
-      <c r="C184" s="8" t="n"/>
-      <c r="D184" s="8" t="n"/>
-      <c r="E184" s="8" t="n"/>
+      <c r="A184" s="9" t="n"/>
+      <c r="B184" s="9" t="n"/>
+      <c r="C184" s="9" t="n"/>
+      <c r="D184" s="9" t="n"/>
+      <c r="E184" s="9" t="n"/>
       <c r="F184" s="4" t="n">
         <v>2</v>
       </c>
@@ -6832,52 +6843,52 @@
       <c r="I184" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J184" s="4" t="inlineStr">
+      <c r="J184" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K184" s="4" t="inlineStr"/>
       <c r="L184" s="4" t="inlineStr"/>
-      <c r="M184" s="8" t="n"/>
+      <c r="M184" s="9" t="n"/>
     </row>
     <row r="185" ht="16" customHeight="1">
-      <c r="A185" s="8" t="n"/>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="8" t="n"/>
-      <c r="D185" s="8" t="n"/>
-      <c r="E185" s="8" t="n"/>
-      <c r="F185" s="9" t="n">
+      <c r="A185" s="9" t="n"/>
+      <c r="B185" s="9" t="n"/>
+      <c r="C185" s="9" t="n"/>
+      <c r="D185" s="9" t="n"/>
+      <c r="E185" s="9" t="n"/>
+      <c r="F185" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G185" s="10" t="inlineStr">
+      <c r="G185" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H185" s="11" t="inlineStr">
+      <c r="H185" s="12" t="inlineStr">
         <is>
           <t>Remoção de gramas mal instaladas</t>
         </is>
       </c>
-      <c r="I185" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J185" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K185" s="9" t="inlineStr"/>
-      <c r="L185" s="9" t="inlineStr"/>
-      <c r="M185" s="8" t="n"/>
+      <c r="I185" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J185" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K185" s="10" t="inlineStr"/>
+      <c r="L185" s="10" t="inlineStr"/>
+      <c r="M185" s="9" t="n"/>
     </row>
     <row r="186" ht="16" customHeight="1">
-      <c r="A186" s="8" t="n"/>
-      <c r="B186" s="8" t="n"/>
-      <c r="C186" s="8" t="n"/>
-      <c r="D186" s="8" t="n"/>
-      <c r="E186" s="8" t="n"/>
+      <c r="A186" s="9" t="n"/>
+      <c r="B186" s="9" t="n"/>
+      <c r="C186" s="9" t="n"/>
+      <c r="D186" s="9" t="n"/>
+      <c r="E186" s="9" t="n"/>
       <c r="F186" s="4" t="n">
         <v>4</v>
       </c>
@@ -6894,52 +6905,52 @@
       <c r="I186" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J186" s="4" t="inlineStr">
+      <c r="J186" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr"/>
       <c r="L186" s="4" t="inlineStr"/>
-      <c r="M186" s="8" t="n"/>
+      <c r="M186" s="9" t="n"/>
     </row>
     <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="8" t="n"/>
-      <c r="B187" s="8" t="n"/>
-      <c r="C187" s="8" t="n"/>
-      <c r="D187" s="8" t="n"/>
-      <c r="E187" s="8" t="n"/>
-      <c r="F187" s="9" t="n">
+      <c r="A187" s="9" t="n"/>
+      <c r="B187" s="9" t="n"/>
+      <c r="C187" s="9" t="n"/>
+      <c r="D187" s="9" t="n"/>
+      <c r="E187" s="9" t="n"/>
+      <c r="F187" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G187" s="10" t="inlineStr">
+      <c r="G187" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H187" s="11" t="inlineStr">
+      <c r="H187" s="12" t="inlineStr">
         <is>
           <t>Replantio das gramas mal instaladas</t>
         </is>
       </c>
-      <c r="I187" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J187" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K187" s="9" t="inlineStr"/>
-      <c r="L187" s="9" t="inlineStr"/>
-      <c r="M187" s="8" t="n"/>
+      <c r="I187" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J187" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K187" s="10" t="inlineStr"/>
+      <c r="L187" s="10" t="inlineStr"/>
+      <c r="M187" s="9" t="n"/>
     </row>
     <row r="188" ht="16" customHeight="1">
-      <c r="A188" s="12" t="n"/>
-      <c r="B188" s="12" t="n"/>
-      <c r="C188" s="12" t="n"/>
-      <c r="D188" s="12" t="n"/>
-      <c r="E188" s="12" t="n"/>
+      <c r="A188" s="14" t="n"/>
+      <c r="B188" s="14" t="n"/>
+      <c r="C188" s="14" t="n"/>
+      <c r="D188" s="14" t="n"/>
+      <c r="E188" s="14" t="n"/>
       <c r="F188" s="4" t="n">
         <v>6</v>
       </c>
@@ -6956,72 +6967,72 @@
       <c r="I188" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J188" s="4" t="inlineStr">
+      <c r="J188" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K188" s="4" t="inlineStr"/>
       <c r="L188" s="4" t="inlineStr"/>
-      <c r="M188" s="12" t="n"/>
+      <c r="M188" s="14" t="n"/>
     </row>
     <row r="189" ht="16" customHeight="1">
-      <c r="A189" s="9" t="n">
+      <c r="A189" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="B189" s="13" t="inlineStr">
+      <c r="B189" s="15" t="inlineStr">
         <is>
           <t>Talude do Fundo da Obra</t>
         </is>
       </c>
-      <c r="C189" s="9" t="inlineStr">
+      <c r="C189" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D189" s="13" t="inlineStr">
+      <c r="D189" s="15" t="inlineStr">
         <is>
           <t>Talude do Fundo da Obra</t>
         </is>
       </c>
-      <c r="E189" s="9" t="n">
+      <c r="E189" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F189" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G189" s="10" t="inlineStr">
+      <c r="F189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G189" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H189" s="11" t="inlineStr">
+      <c r="H189" s="12" t="inlineStr">
         <is>
           <t>Realinhamento da grama</t>
         </is>
       </c>
-      <c r="I189" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J189" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K189" s="9" t="inlineStr"/>
-      <c r="L189" s="9" t="inlineStr"/>
-      <c r="M189" s="9" t="inlineStr">
+      <c r="I189" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J189" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K189" s="10" t="inlineStr"/>
+      <c r="L189" s="10" t="inlineStr"/>
+      <c r="M189" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="190" ht="16" customHeight="1">
-      <c r="A190" s="8" t="n"/>
-      <c r="B190" s="8" t="n"/>
-      <c r="C190" s="8" t="n"/>
-      <c r="D190" s="8" t="n"/>
-      <c r="E190" s="8" t="n"/>
+      <c r="A190" s="9" t="n"/>
+      <c r="B190" s="9" t="n"/>
+      <c r="C190" s="9" t="n"/>
+      <c r="D190" s="9" t="n"/>
+      <c r="E190" s="9" t="n"/>
       <c r="F190" s="4" t="n">
         <v>2</v>
       </c>
@@ -7038,52 +7049,52 @@
       <c r="I190" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J190" s="4" t="inlineStr">
+      <c r="J190" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K190" s="4" t="inlineStr"/>
       <c r="L190" s="4" t="inlineStr"/>
-      <c r="M190" s="8" t="n"/>
+      <c r="M190" s="9" t="n"/>
     </row>
     <row r="191" ht="16" customHeight="1">
-      <c r="A191" s="8" t="n"/>
-      <c r="B191" s="8" t="n"/>
-      <c r="C191" s="8" t="n"/>
-      <c r="D191" s="8" t="n"/>
-      <c r="E191" s="8" t="n"/>
-      <c r="F191" s="9" t="n">
+      <c r="A191" s="9" t="n"/>
+      <c r="B191" s="9" t="n"/>
+      <c r="C191" s="9" t="n"/>
+      <c r="D191" s="9" t="n"/>
+      <c r="E191" s="9" t="n"/>
+      <c r="F191" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G191" s="10" t="inlineStr">
+      <c r="G191" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H191" s="11" t="inlineStr">
+      <c r="H191" s="12" t="inlineStr">
         <is>
           <t>Remoção de gramas mal instaladas</t>
         </is>
       </c>
-      <c r="I191" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J191" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K191" s="9" t="inlineStr"/>
-      <c r="L191" s="9" t="inlineStr"/>
-      <c r="M191" s="8" t="n"/>
+      <c r="I191" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J191" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K191" s="10" t="inlineStr"/>
+      <c r="L191" s="10" t="inlineStr"/>
+      <c r="M191" s="9" t="n"/>
     </row>
     <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="8" t="n"/>
-      <c r="B192" s="8" t="n"/>
-      <c r="C192" s="8" t="n"/>
-      <c r="D192" s="8" t="n"/>
-      <c r="E192" s="8" t="n"/>
+      <c r="A192" s="9" t="n"/>
+      <c r="B192" s="9" t="n"/>
+      <c r="C192" s="9" t="n"/>
+      <c r="D192" s="9" t="n"/>
+      <c r="E192" s="9" t="n"/>
       <c r="F192" s="4" t="n">
         <v>4</v>
       </c>
@@ -7100,52 +7111,52 @@
       <c r="I192" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J192" s="4" t="inlineStr">
+      <c r="J192" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr"/>
       <c r="L192" s="4" t="inlineStr"/>
-      <c r="M192" s="8" t="n"/>
+      <c r="M192" s="9" t="n"/>
     </row>
     <row r="193" ht="16" customHeight="1">
-      <c r="A193" s="8" t="n"/>
-      <c r="B193" s="8" t="n"/>
-      <c r="C193" s="8" t="n"/>
-      <c r="D193" s="8" t="n"/>
-      <c r="E193" s="8" t="n"/>
-      <c r="F193" s="9" t="n">
+      <c r="A193" s="9" t="n"/>
+      <c r="B193" s="9" t="n"/>
+      <c r="C193" s="9" t="n"/>
+      <c r="D193" s="9" t="n"/>
+      <c r="E193" s="9" t="n"/>
+      <c r="F193" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G193" s="10" t="inlineStr">
+      <c r="G193" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H193" s="11" t="inlineStr">
+      <c r="H193" s="12" t="inlineStr">
         <is>
           <t>Replantio das gramas mal instaladas</t>
         </is>
       </c>
-      <c r="I193" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J193" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K193" s="9" t="inlineStr"/>
-      <c r="L193" s="9" t="inlineStr"/>
-      <c r="M193" s="8" t="n"/>
+      <c r="I193" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J193" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K193" s="10" t="inlineStr"/>
+      <c r="L193" s="10" t="inlineStr"/>
+      <c r="M193" s="9" t="n"/>
     </row>
     <row r="194" ht="16" customHeight="1">
-      <c r="A194" s="12" t="n"/>
-      <c r="B194" s="12" t="n"/>
-      <c r="C194" s="12" t="n"/>
-      <c r="D194" s="12" t="n"/>
-      <c r="E194" s="12" t="n"/>
+      <c r="A194" s="14" t="n"/>
+      <c r="B194" s="14" t="n"/>
+      <c r="C194" s="14" t="n"/>
+      <c r="D194" s="14" t="n"/>
+      <c r="E194" s="14" t="n"/>
       <c r="F194" s="4" t="n">
         <v>6</v>
       </c>
@@ -7162,72 +7173,72 @@
       <c r="I194" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J194" s="4" t="inlineStr">
+      <c r="J194" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K194" s="4" t="inlineStr"/>
       <c r="L194" s="4" t="inlineStr"/>
-      <c r="M194" s="12" t="n"/>
+      <c r="M194" s="14" t="n"/>
     </row>
     <row r="195" ht="16" customHeight="1">
-      <c r="A195" s="9" t="n">
+      <c r="A195" s="10" t="n">
         <v>31</v>
       </c>
-      <c r="B195" s="13" t="inlineStr">
+      <c r="B195" s="15" t="inlineStr">
         <is>
           <t>Talude do Fundo da Obra</t>
         </is>
       </c>
-      <c r="C195" s="9" t="inlineStr">
+      <c r="C195" s="10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D195" s="13" t="inlineStr">
+      <c r="D195" s="15" t="inlineStr">
         <is>
           <t>Talude do Fundo da Obra</t>
         </is>
       </c>
-      <c r="E195" s="9" t="n">
+      <c r="E195" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F195" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G195" s="10" t="inlineStr">
+      <c r="F195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H195" s="11" t="inlineStr">
+      <c r="H195" s="12" t="inlineStr">
         <is>
           <t>Realinhamento da grama</t>
         </is>
       </c>
-      <c r="I195" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J195" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K195" s="9" t="inlineStr"/>
-      <c r="L195" s="9" t="inlineStr"/>
-      <c r="M195" s="9" t="inlineStr">
+      <c r="I195" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J195" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K195" s="10" t="inlineStr"/>
+      <c r="L195" s="10" t="inlineStr"/>
+      <c r="M195" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="196" ht="16" customHeight="1">
-      <c r="A196" s="8" t="n"/>
-      <c r="B196" s="8" t="n"/>
-      <c r="C196" s="8" t="n"/>
-      <c r="D196" s="8" t="n"/>
-      <c r="E196" s="8" t="n"/>
+      <c r="A196" s="9" t="n"/>
+      <c r="B196" s="9" t="n"/>
+      <c r="C196" s="9" t="n"/>
+      <c r="D196" s="9" t="n"/>
+      <c r="E196" s="9" t="n"/>
       <c r="F196" s="4" t="n">
         <v>2</v>
       </c>
@@ -7244,52 +7255,52 @@
       <c r="I196" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J196" s="4" t="inlineStr">
+      <c r="J196" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K196" s="4" t="inlineStr"/>
       <c r="L196" s="4" t="inlineStr"/>
-      <c r="M196" s="8" t="n"/>
+      <c r="M196" s="9" t="n"/>
     </row>
     <row r="197" ht="16" customHeight="1">
-      <c r="A197" s="8" t="n"/>
-      <c r="B197" s="8" t="n"/>
-      <c r="C197" s="8" t="n"/>
-      <c r="D197" s="8" t="n"/>
-      <c r="E197" s="8" t="n"/>
-      <c r="F197" s="9" t="n">
+      <c r="A197" s="9" t="n"/>
+      <c r="B197" s="9" t="n"/>
+      <c r="C197" s="9" t="n"/>
+      <c r="D197" s="9" t="n"/>
+      <c r="E197" s="9" t="n"/>
+      <c r="F197" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G197" s="10" t="inlineStr">
+      <c r="G197" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H197" s="11" t="inlineStr">
+      <c r="H197" s="12" t="inlineStr">
         <is>
           <t>Remoção de gramas mal instaladas</t>
         </is>
       </c>
-      <c r="I197" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J197" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K197" s="9" t="inlineStr"/>
-      <c r="L197" s="9" t="inlineStr"/>
-      <c r="M197" s="8" t="n"/>
+      <c r="I197" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K197" s="10" t="inlineStr"/>
+      <c r="L197" s="10" t="inlineStr"/>
+      <c r="M197" s="9" t="n"/>
     </row>
     <row r="198" ht="16" customHeight="1">
-      <c r="A198" s="8" t="n"/>
-      <c r="B198" s="8" t="n"/>
-      <c r="C198" s="8" t="n"/>
-      <c r="D198" s="8" t="n"/>
-      <c r="E198" s="8" t="n"/>
+      <c r="A198" s="9" t="n"/>
+      <c r="B198" s="9" t="n"/>
+      <c r="C198" s="9" t="n"/>
+      <c r="D198" s="9" t="n"/>
+      <c r="E198" s="9" t="n"/>
       <c r="F198" s="4" t="n">
         <v>4</v>
       </c>
@@ -7306,52 +7317,52 @@
       <c r="I198" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J198" s="4" t="inlineStr">
+      <c r="J198" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K198" s="4" t="inlineStr"/>
       <c r="L198" s="4" t="inlineStr"/>
-      <c r="M198" s="8" t="n"/>
+      <c r="M198" s="9" t="n"/>
     </row>
     <row r="199" ht="16" customHeight="1">
-      <c r="A199" s="8" t="n"/>
-      <c r="B199" s="8" t="n"/>
-      <c r="C199" s="8" t="n"/>
-      <c r="D199" s="8" t="n"/>
-      <c r="E199" s="8" t="n"/>
-      <c r="F199" s="9" t="n">
+      <c r="A199" s="9" t="n"/>
+      <c r="B199" s="9" t="n"/>
+      <c r="C199" s="9" t="n"/>
+      <c r="D199" s="9" t="n"/>
+      <c r="E199" s="9" t="n"/>
+      <c r="F199" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G199" s="10" t="inlineStr">
+      <c r="G199" s="11" t="inlineStr">
         <is>
           <t>Plantio de Grama</t>
         </is>
       </c>
-      <c r="H199" s="11" t="inlineStr">
+      <c r="H199" s="12" t="inlineStr">
         <is>
           <t>Replantio das gramas mal instaladas</t>
         </is>
       </c>
-      <c r="I199" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J199" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K199" s="9" t="inlineStr"/>
-      <c r="L199" s="9" t="inlineStr"/>
-      <c r="M199" s="8" t="n"/>
+      <c r="I199" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J199" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K199" s="10" t="inlineStr"/>
+      <c r="L199" s="10" t="inlineStr"/>
+      <c r="M199" s="9" t="n"/>
     </row>
     <row r="200" ht="16" customHeight="1">
-      <c r="A200" s="12" t="n"/>
-      <c r="B200" s="12" t="n"/>
-      <c r="C200" s="12" t="n"/>
-      <c r="D200" s="12" t="n"/>
-      <c r="E200" s="12" t="n"/>
+      <c r="A200" s="14" t="n"/>
+      <c r="B200" s="14" t="n"/>
+      <c r="C200" s="14" t="n"/>
+      <c r="D200" s="14" t="n"/>
+      <c r="E200" s="14" t="n"/>
       <c r="F200" s="4" t="n">
         <v>6</v>
       </c>
@@ -7368,72 +7379,72 @@
       <c r="I200" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J200" s="4" t="inlineStr">
+      <c r="J200" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K200" s="4" t="inlineStr"/>
       <c r="L200" s="4" t="inlineStr"/>
-      <c r="M200" s="12" t="n"/>
+      <c r="M200" s="14" t="n"/>
     </row>
     <row r="201" ht="16" customHeight="1">
-      <c r="A201" s="9" t="n">
+      <c r="A201" s="10" t="n">
         <v>32</v>
       </c>
-      <c r="B201" s="13" t="inlineStr">
+      <c r="B201" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="C201" s="9" t="inlineStr">
+      <c r="C201" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D201" s="13" t="inlineStr">
+      <c r="D201" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="E201" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F201" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G201" s="10" t="inlineStr">
+      <c r="E201" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G201" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H201" s="11" t="inlineStr">
+      <c r="H201" s="12" t="inlineStr">
         <is>
           <t>Remoção de materiais espalhados</t>
         </is>
       </c>
-      <c r="I201" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J201" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K201" s="9" t="inlineStr"/>
-      <c r="L201" s="9" t="inlineStr"/>
-      <c r="M201" s="9" t="inlineStr">
+      <c r="I201" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K201" s="10" t="inlineStr"/>
+      <c r="L201" s="10" t="inlineStr"/>
+      <c r="M201" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="202" ht="16" customHeight="1">
-      <c r="A202" s="12" t="n"/>
-      <c r="B202" s="12" t="n"/>
-      <c r="C202" s="12" t="n"/>
-      <c r="D202" s="12" t="n"/>
-      <c r="E202" s="12" t="n"/>
+      <c r="A202" s="14" t="n"/>
+      <c r="B202" s="14" t="n"/>
+      <c r="C202" s="14" t="n"/>
+      <c r="D202" s="14" t="n"/>
+      <c r="E202" s="14" t="n"/>
       <c r="F202" s="4" t="n">
         <v>2</v>
       </c>
@@ -7450,72 +7461,72 @@
       <c r="I202" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J202" s="4" t="inlineStr">
+      <c r="J202" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K202" s="4" t="inlineStr"/>
       <c r="L202" s="4" t="inlineStr"/>
-      <c r="M202" s="12" t="n"/>
+      <c r="M202" s="14" t="n"/>
     </row>
     <row r="203" ht="16" customHeight="1">
-      <c r="A203" s="9" t="n">
+      <c r="A203" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="B203" s="13" t="inlineStr">
+      <c r="B203" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="C203" s="9" t="inlineStr">
+      <c r="C203" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D203" s="13" t="inlineStr">
+      <c r="D203" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="E203" s="9" t="n">
+      <c r="E203" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="F203" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G203" s="10" t="inlineStr">
+      <c r="F203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G203" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H203" s="11" t="inlineStr">
+      <c r="H203" s="12" t="inlineStr">
         <is>
           <t>Remoção de materiais espalhados</t>
         </is>
       </c>
-      <c r="I203" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J203" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K203" s="9" t="inlineStr"/>
-      <c r="L203" s="9" t="inlineStr"/>
-      <c r="M203" s="9" t="inlineStr">
+      <c r="I203" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J203" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K203" s="10" t="inlineStr"/>
+      <c r="L203" s="10" t="inlineStr"/>
+      <c r="M203" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="204" ht="16" customHeight="1">
-      <c r="A204" s="12" t="n"/>
-      <c r="B204" s="12" t="n"/>
-      <c r="C204" s="12" t="n"/>
-      <c r="D204" s="12" t="n"/>
-      <c r="E204" s="12" t="n"/>
+      <c r="A204" s="14" t="n"/>
+      <c r="B204" s="14" t="n"/>
+      <c r="C204" s="14" t="n"/>
+      <c r="D204" s="14" t="n"/>
+      <c r="E204" s="14" t="n"/>
       <c r="F204" s="4" t="n">
         <v>2</v>
       </c>
@@ -7532,72 +7543,72 @@
       <c r="I204" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J204" s="4" t="inlineStr">
+      <c r="J204" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K204" s="4" t="inlineStr"/>
       <c r="L204" s="4" t="inlineStr"/>
-      <c r="M204" s="12" t="n"/>
+      <c r="M204" s="14" t="n"/>
     </row>
     <row r="205" ht="16" customHeight="1">
-      <c r="A205" s="9" t="n">
+      <c r="A205" s="10" t="n">
         <v>34</v>
       </c>
-      <c r="B205" s="13" t="inlineStr">
+      <c r="B205" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="C205" s="9" t="inlineStr">
+      <c r="C205" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D205" s="13" t="inlineStr">
+      <c r="D205" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="E205" s="9" t="n">
+      <c r="E205" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F205" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G205" s="10" t="inlineStr">
+      <c r="F205" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G205" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H205" s="11" t="inlineStr">
+      <c r="H205" s="12" t="inlineStr">
         <is>
           <t>Remoção de materiais espalhados</t>
         </is>
       </c>
-      <c r="I205" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J205" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K205" s="9" t="inlineStr"/>
-      <c r="L205" s="9" t="inlineStr"/>
-      <c r="M205" s="9" t="inlineStr">
+      <c r="I205" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J205" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K205" s="10" t="inlineStr"/>
+      <c r="L205" s="10" t="inlineStr"/>
+      <c r="M205" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="206" ht="16" customHeight="1">
-      <c r="A206" s="12" t="n"/>
-      <c r="B206" s="12" t="n"/>
-      <c r="C206" s="12" t="n"/>
-      <c r="D206" s="12" t="n"/>
-      <c r="E206" s="12" t="n"/>
+      <c r="A206" s="14" t="n"/>
+      <c r="B206" s="14" t="n"/>
+      <c r="C206" s="14" t="n"/>
+      <c r="D206" s="14" t="n"/>
+      <c r="E206" s="14" t="n"/>
       <c r="F206" s="4" t="n">
         <v>2</v>
       </c>
@@ -7614,72 +7625,72 @@
       <c r="I206" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J206" s="4" t="inlineStr">
+      <c r="J206" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K206" s="4" t="inlineStr"/>
       <c r="L206" s="4" t="inlineStr"/>
-      <c r="M206" s="12" t="n"/>
+      <c r="M206" s="14" t="n"/>
     </row>
     <row r="207" ht="16" customHeight="1">
-      <c r="A207" s="9" t="n">
+      <c r="A207" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="B207" s="13" t="inlineStr">
+      <c r="B207" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="C207" s="9" t="inlineStr">
+      <c r="C207" s="10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D207" s="13" t="inlineStr">
+      <c r="D207" s="15" t="inlineStr">
         <is>
           <t>Platô — Frente ao Prédio Administrativo</t>
         </is>
       </c>
-      <c r="E207" s="9" t="n">
+      <c r="E207" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F207" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G207" s="10" t="inlineStr">
+      <c r="F207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H207" s="11" t="inlineStr">
+      <c r="H207" s="12" t="inlineStr">
         <is>
           <t>Remoção de materiais espalhados</t>
         </is>
       </c>
-      <c r="I207" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J207" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K207" s="9" t="inlineStr"/>
-      <c r="L207" s="9" t="inlineStr"/>
-      <c r="M207" s="9" t="inlineStr">
+      <c r="I207" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J207" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K207" s="10" t="inlineStr"/>
+      <c r="L207" s="10" t="inlineStr"/>
+      <c r="M207" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="208" ht="16" customHeight="1">
-      <c r="A208" s="12" t="n"/>
-      <c r="B208" s="12" t="n"/>
-      <c r="C208" s="12" t="n"/>
-      <c r="D208" s="12" t="n"/>
-      <c r="E208" s="12" t="n"/>
+      <c r="A208" s="14" t="n"/>
+      <c r="B208" s="14" t="n"/>
+      <c r="C208" s="14" t="n"/>
+      <c r="D208" s="14" t="n"/>
+      <c r="E208" s="14" t="n"/>
       <c r="F208" s="4" t="n">
         <v>2</v>
       </c>
@@ -7696,72 +7707,72 @@
       <c r="I208" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J208" s="4" t="inlineStr">
+      <c r="J208" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K208" s="4" t="inlineStr"/>
       <c r="L208" s="4" t="inlineStr"/>
-      <c r="M208" s="12" t="n"/>
+      <c r="M208" s="14" t="n"/>
     </row>
     <row r="209" ht="16" customHeight="1">
-      <c r="A209" s="9" t="n">
+      <c r="A209" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="B209" s="13" t="inlineStr">
+      <c r="B209" s="15" t="inlineStr">
         <is>
           <t>Platô Central</t>
         </is>
       </c>
-      <c r="C209" s="9" t="inlineStr">
+      <c r="C209" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D209" s="13" t="inlineStr">
+      <c r="D209" s="15" t="inlineStr">
         <is>
           <t>Platô Central</t>
         </is>
       </c>
-      <c r="E209" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F209" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G209" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H209" s="11" t="inlineStr">
+      <c r="E209" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G209" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H209" s="12" t="inlineStr">
         <is>
           <t>Remoção de Canaletas</t>
         </is>
       </c>
-      <c r="I209" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J209" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K209" s="9" t="inlineStr"/>
-      <c r="L209" s="9" t="inlineStr"/>
-      <c r="M209" s="9" t="inlineStr">
+      <c r="I209" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K209" s="10" t="inlineStr"/>
+      <c r="L209" s="10" t="inlineStr"/>
+      <c r="M209" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="210" ht="16" customHeight="1">
-      <c r="A210" s="8" t="n"/>
-      <c r="B210" s="8" t="n"/>
-      <c r="C210" s="8" t="n"/>
-      <c r="D210" s="8" t="n"/>
-      <c r="E210" s="8" t="n"/>
+      <c r="A210" s="9" t="n"/>
+      <c r="B210" s="9" t="n"/>
+      <c r="C210" s="9" t="n"/>
+      <c r="D210" s="9" t="n"/>
+      <c r="E210" s="9" t="n"/>
       <c r="F210" s="4" t="n">
         <v>2</v>
       </c>
@@ -7778,45 +7789,45 @@
       <c r="I210" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J210" s="4" t="inlineStr">
+      <c r="J210" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K210" s="4" t="inlineStr"/>
       <c r="L210" s="4" t="inlineStr"/>
-      <c r="M210" s="8" t="n"/>
+      <c r="M210" s="9" t="n"/>
     </row>
     <row r="211" ht="16" customHeight="1">
-      <c r="A211" s="12" t="n"/>
-      <c r="B211" s="12" t="n"/>
-      <c r="C211" s="12" t="n"/>
-      <c r="D211" s="12" t="n"/>
-      <c r="E211" s="12" t="n"/>
-      <c r="F211" s="9" t="n">
+      <c r="A211" s="14" t="n"/>
+      <c r="B211" s="14" t="n"/>
+      <c r="C211" s="14" t="n"/>
+      <c r="D211" s="14" t="n"/>
+      <c r="E211" s="14" t="n"/>
+      <c r="F211" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G211" s="10" t="inlineStr">
+      <c r="G211" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H211" s="11" t="inlineStr">
+      <c r="H211" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I211" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J211" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K211" s="9" t="inlineStr"/>
-      <c r="L211" s="9" t="inlineStr"/>
-      <c r="M211" s="12" t="n"/>
+      <c r="I211" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J211" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K211" s="10" t="inlineStr"/>
+      <c r="L211" s="10" t="inlineStr"/>
+      <c r="M211" s="14" t="n"/>
     </row>
     <row r="212" ht="16" customHeight="1">
       <c r="A212" s="4" t="n">
@@ -7856,56 +7867,56 @@
       <c r="I212" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J212" s="4" t="inlineStr">
+      <c r="J212" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K212" s="4" t="inlineStr"/>
       <c r="L212" s="4" t="inlineStr"/>
-      <c r="M212" s="4" t="inlineStr">
+      <c r="M212" s="8" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="213" ht="16" customHeight="1">
-      <c r="A213" s="8" t="n"/>
-      <c r="B213" s="8" t="n"/>
-      <c r="C213" s="8" t="n"/>
-      <c r="D213" s="8" t="n"/>
-      <c r="E213" s="8" t="n"/>
-      <c r="F213" s="9" t="n">
+      <c r="A213" s="9" t="n"/>
+      <c r="B213" s="9" t="n"/>
+      <c r="C213" s="9" t="n"/>
+      <c r="D213" s="9" t="n"/>
+      <c r="E213" s="9" t="n"/>
+      <c r="F213" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G213" s="10" t="inlineStr">
+      <c r="G213" s="11" t="inlineStr">
         <is>
           <t>Terraplanagem</t>
         </is>
       </c>
-      <c r="H213" s="11" t="inlineStr">
+      <c r="H213" s="12" t="inlineStr">
         <is>
           <t>Regularização e adensamento do Platôr Central</t>
         </is>
       </c>
-      <c r="I213" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J213" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K213" s="9" t="inlineStr"/>
-      <c r="L213" s="9" t="inlineStr"/>
-      <c r="M213" s="8" t="n"/>
+      <c r="I213" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J213" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K213" s="10" t="inlineStr"/>
+      <c r="L213" s="10" t="inlineStr"/>
+      <c r="M213" s="9" t="n"/>
     </row>
     <row r="214" ht="16" customHeight="1">
-      <c r="A214" s="12" t="n"/>
-      <c r="B214" s="12" t="n"/>
-      <c r="C214" s="12" t="n"/>
-      <c r="D214" s="12" t="n"/>
-      <c r="E214" s="12" t="n"/>
+      <c r="A214" s="14" t="n"/>
+      <c r="B214" s="14" t="n"/>
+      <c r="C214" s="14" t="n"/>
+      <c r="D214" s="14" t="n"/>
+      <c r="E214" s="14" t="n"/>
       <c r="F214" s="4" t="n">
         <v>3</v>
       </c>
@@ -7922,72 +7933,72 @@
       <c r="I214" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J214" s="4" t="inlineStr">
+      <c r="J214" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K214" s="4" t="inlineStr"/>
       <c r="L214" s="4" t="inlineStr"/>
-      <c r="M214" s="12" t="n"/>
+      <c r="M214" s="14" t="n"/>
     </row>
     <row r="215" ht="16" customHeight="1">
-      <c r="A215" s="9" t="n">
+      <c r="A215" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="B215" s="13" t="inlineStr">
+      <c r="B215" s="15" t="inlineStr">
         <is>
           <t>Platô Central</t>
         </is>
       </c>
-      <c r="C215" s="9" t="inlineStr">
+      <c r="C215" s="10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D215" s="13" t="inlineStr">
+      <c r="D215" s="15" t="inlineStr">
         <is>
           <t>Platô Central</t>
         </is>
       </c>
-      <c r="E215" s="9" t="n">
+      <c r="E215" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="F215" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G215" s="10" t="inlineStr">
-        <is>
-          <t>Macrodrenagem</t>
-        </is>
-      </c>
-      <c r="H215" s="11" t="inlineStr">
+      <c r="F215" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G215" s="11" t="inlineStr">
+        <is>
+          <t>Macrodrenagem</t>
+        </is>
+      </c>
+      <c r="H215" s="12" t="inlineStr">
         <is>
           <t>Remoção de Canaletas</t>
         </is>
       </c>
-      <c r="I215" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J215" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K215" s="9" t="inlineStr"/>
-      <c r="L215" s="9" t="inlineStr"/>
-      <c r="M215" s="9" t="inlineStr">
+      <c r="I215" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J215" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K215" s="10" t="inlineStr"/>
+      <c r="L215" s="10" t="inlineStr"/>
+      <c r="M215" s="13" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="216" ht="16" customHeight="1">
-      <c r="A216" s="8" t="n"/>
-      <c r="B216" s="8" t="n"/>
-      <c r="C216" s="8" t="n"/>
-      <c r="D216" s="8" t="n"/>
-      <c r="E216" s="8" t="n"/>
+      <c r="A216" s="9" t="n"/>
+      <c r="B216" s="9" t="n"/>
+      <c r="C216" s="9" t="n"/>
+      <c r="D216" s="9" t="n"/>
+      <c r="E216" s="9" t="n"/>
       <c r="F216" s="4" t="n">
         <v>2</v>
       </c>
@@ -8004,45 +8015,45 @@
       <c r="I216" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J216" s="4" t="inlineStr">
+      <c r="J216" s="8" t="inlineStr">
         <is>
           <t>Pendente</t>
         </is>
       </c>
       <c r="K216" s="4" t="inlineStr"/>
       <c r="L216" s="4" t="inlineStr"/>
-      <c r="M216" s="8" t="n"/>
+      <c r="M216" s="9" t="n"/>
     </row>
     <row r="217" ht="16" customHeight="1">
-      <c r="A217" s="12" t="n"/>
-      <c r="B217" s="12" t="n"/>
-      <c r="C217" s="12" t="n"/>
-      <c r="D217" s="12" t="n"/>
-      <c r="E217" s="12" t="n"/>
-      <c r="F217" s="9" t="n">
+      <c r="A217" s="14" t="n"/>
+      <c r="B217" s="14" t="n"/>
+      <c r="C217" s="14" t="n"/>
+      <c r="D217" s="14" t="n"/>
+      <c r="E217" s="14" t="n"/>
+      <c r="F217" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G217" s="10" t="inlineStr">
+      <c r="G217" s="11" t="inlineStr">
         <is>
           <t>Geral / 5S</t>
         </is>
       </c>
-      <c r="H217" s="11" t="inlineStr">
+      <c r="H217" s="12" t="inlineStr">
         <is>
           <t>Limpeza geral e reorganização da área</t>
         </is>
       </c>
-      <c r="I217" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J217" s="9" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K217" s="9" t="inlineStr"/>
-      <c r="L217" s="9" t="inlineStr"/>
-      <c r="M217" s="12" t="n"/>
+      <c r="I217" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J217" s="13" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K217" s="10" t="inlineStr"/>
+      <c r="L217" s="10" t="inlineStr"/>
+      <c r="M217" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="230">

--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -28,32 +28,32 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000BCD4"/>
+      <color rgb="00FFFFFF"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="007BAFD4"/>
+      <color rgb="001A3A6A"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="0000BCD4"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00C8D8F0"/>
+      <color rgb="001A2A40"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="00B0BEC5"/>
+      <color rgb="005A7090"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -62,22 +62,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000A1628"/>
+        <fgColor rgb="001A3A6A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D2540"/>
+        <fgColor rgb="00D6E4F7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000D1A30"/>
+        <fgColor rgb="001E4D99"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00081020"/>
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEF4FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,35 +96,35 @@
     </border>
     <border>
       <left style="medium">
-        <color rgb="0000BCD4"/>
+        <color rgb="001E4D99"/>
       </left>
       <right style="medium">
-        <color rgb="0000BCD4"/>
+        <color rgb="001E4D99"/>
       </right>
       <top style="medium">
-        <color rgb="0000BCD4"/>
+        <color rgb="001E4D99"/>
       </top>
       <bottom style="medium">
-        <color rgb="0000BCD4"/>
+        <color rgb="001E4D99"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </left>
       <right style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </right>
       <top style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </top>
       <bottom style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </bottom>
     </border>
     <border>
       <left style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </left>
       <right/>
       <top/>
@@ -128,10 +133,10 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </left>
       <right style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </right>
       <top/>
       <bottom/>
@@ -139,14 +144,14 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </left>
       <right style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color rgb="001A3A60"/>
+        <color rgb="00BDD0E8"/>
       </bottom>
       <diagonal/>
     </border>
@@ -162,27 +167,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -193,8 +185,21 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -559,6 +564,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -574,27 +580,27 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>PUSH LIST — SERVIÇOS DAENG | ASU JUNDIAÍ (26001) | OTZ Engenharia × Messer Gases for Life</t>
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV3 — 03/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>#Card</t>

--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -623,7 +623,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV3 — 07/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
+          <t>Ref: CLM-216  |  Contratada: Andrade e Rocha (DAENG)  |  Gerenciadora: OTZ Engenharia — GPLAN  |  Levantamento: 02/07/2026  |  REV3 — 08/07/2026  |  Elaborado por: Ilson do Santos Azevedo / Supervisor de Planejamento</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,11 @@
           <t>Concluída</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
       <c r="L4" s="9" t="inlineStr">
         <is>
           <t>33.3%</t>
@@ -927,15 +931,19 @@
       <c r="I10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="14" t="inlineStr">
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -1072,10 +1080,14 @@
           <t>Concluída</t>
         </is>
       </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="9" t="inlineStr">
+      <c r="K14" s="4" t="inlineStr">
         <is>
           <t>44.4%</t>
+        </is>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -1131,9 +1143,9 @@
       <c r="I16" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J16" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr"/>
@@ -1191,9 +1203,9 @@
       <c r="I18" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J18" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -1362,10 +1374,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K23" s="11" t="inlineStr"/>
-      <c r="L23" s="15" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L23" s="9" t="inlineStr">
+        <is>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -1391,9 +1407,9 @@
       <c r="I24" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J24" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr"/>
@@ -1571,9 +1587,9 @@
       <c r="I30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr"/>
@@ -1652,7 +1668,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -1792,10 +1812,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="14" t="inlineStr">
+      <c r="K36" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L36" s="9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1821,9 +1845,9 @@
       <c r="I37" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
@@ -1902,10 +1926,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K39" s="11" t="inlineStr"/>
-      <c r="L39" s="15" t="inlineStr">
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L39" s="9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1931,9 +1959,9 @@
       <c r="I40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr"/>
@@ -2007,15 +2035,19 @@
       <c r="I42" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="14" t="inlineStr">
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
+        <is>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -2041,9 +2073,9 @@
       <c r="I43" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr"/>
@@ -2071,9 +2103,9 @@
       <c r="I44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J44" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr"/>
@@ -2152,7 +2184,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -2352,7 +2388,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -2582,7 +2622,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K59" s="11" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L59" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -2722,7 +2766,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K63" s="11" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L63" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -2862,7 +2910,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L67" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -3212,7 +3264,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -3562,7 +3618,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K89" s="11" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L89" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -3792,10 +3852,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K96" s="4" t="inlineStr"/>
-      <c r="L96" s="14" t="inlineStr">
+      <c r="K96" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L96" s="9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -3941,9 +4005,9 @@
       <c r="I101" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J101" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J101" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K101" s="11" t="inlineStr"/>
@@ -3971,9 +4035,9 @@
       <c r="I102" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J102" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J102" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K102" s="4" t="inlineStr"/>
@@ -4142,10 +4206,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K107" s="11" t="inlineStr"/>
-      <c r="L107" s="15" t="inlineStr">
+      <c r="K107" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -4171,9 +4239,9 @@
       <c r="I108" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J108" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J108" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr"/>
@@ -4261,9 +4329,9 @@
       <c r="I111" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J111" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J111" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K111" s="11" t="inlineStr"/>
@@ -4372,10 +4440,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K114" s="4" t="inlineStr"/>
-      <c r="L114" s="14" t="inlineStr">
+      <c r="K114" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L114" s="9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -4431,9 +4503,9 @@
       <c r="I116" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J116" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J116" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K116" s="4" t="inlineStr"/>
@@ -4491,9 +4563,9 @@
       <c r="I118" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J118" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J118" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr"/>
@@ -4602,10 +4674,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K121" s="11" t="inlineStr"/>
-      <c r="L121" s="15" t="inlineStr">
+      <c r="K121" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L121" s="9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -4751,9 +4827,9 @@
       <c r="I126" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J126" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J126" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K126" s="4" t="inlineStr"/>
@@ -4841,9 +4917,9 @@
       <c r="I129" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J129" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J129" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K129" s="11" t="inlineStr"/>
@@ -4952,10 +5028,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K132" s="4" t="inlineStr"/>
-      <c r="L132" s="14" t="inlineStr">
+      <c r="K132" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L132" s="9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -4981,9 +5061,9 @@
       <c r="I133" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J133" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J133" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K133" s="11" t="inlineStr"/>
@@ -5071,9 +5151,9 @@
       <c r="I136" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J136" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J136" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K136" s="4" t="inlineStr"/>
@@ -5182,10 +5262,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K139" s="11" t="inlineStr"/>
-      <c r="L139" s="15" t="inlineStr">
+      <c r="K139" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L139" s="9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -5211,9 +5295,9 @@
       <c r="I140" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J140" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J140" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K140" s="4" t="inlineStr"/>
@@ -5301,9 +5385,9 @@
       <c r="I143" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J143" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J143" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K143" s="11" t="inlineStr"/>
@@ -5412,10 +5496,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K146" s="4" t="inlineStr"/>
-      <c r="L146" s="14" t="inlineStr">
+      <c r="K146" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L146" s="9" t="inlineStr">
+        <is>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -5441,9 +5529,9 @@
       <c r="I147" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J147" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J147" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K147" s="11" t="inlineStr"/>
@@ -5531,9 +5619,9 @@
       <c r="I150" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J150" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J150" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K150" s="4" t="inlineStr"/>
@@ -5642,10 +5730,14 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K153" s="11" t="inlineStr"/>
-      <c r="L153" s="15" t="inlineStr">
+      <c r="K153" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L153" s="9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -5791,9 +5883,9 @@
       <c r="I158" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J158" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J158" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K158" s="4" t="inlineStr"/>
@@ -5881,9 +5973,9 @@
       <c r="I161" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J161" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J161" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K161" s="11" t="inlineStr"/>
@@ -5992,7 +6084,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K164" s="4" t="inlineStr"/>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L164" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -6192,7 +6288,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K170" s="4" t="inlineStr"/>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L170" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -6302,7 +6402,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K173" s="11" t="inlineStr"/>
+      <c r="K173" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L173" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -6412,7 +6516,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K176" s="4" t="inlineStr"/>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L176" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -6517,15 +6625,19 @@
       <c r="I179" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J179" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K179" s="11" t="inlineStr"/>
-      <c r="L179" s="15" t="inlineStr">
+      <c r="J179" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K179" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L179" s="8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6551,9 +6663,9 @@
       <c r="I180" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J180" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J180" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K180" s="4" t="inlineStr"/>
@@ -6581,9 +6693,9 @@
       <c r="I181" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J181" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J181" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K181" s="11" t="inlineStr"/>
@@ -6641,9 +6753,9 @@
       <c r="I183" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J183" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J183" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K183" s="11" t="inlineStr"/>
@@ -6717,15 +6829,19 @@
       <c r="I185" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J185" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K185" s="11" t="inlineStr"/>
-      <c r="L185" s="15" t="inlineStr">
+      <c r="J185" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K185" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L185" s="8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6751,9 +6867,9 @@
       <c r="I186" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J186" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J186" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K186" s="4" t="inlineStr"/>
@@ -6781,9 +6897,9 @@
       <c r="I187" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J187" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J187" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K187" s="11" t="inlineStr"/>
@@ -6841,9 +6957,9 @@
       <c r="I189" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J189" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J189" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K189" s="11" t="inlineStr"/>
@@ -6917,15 +7033,19 @@
       <c r="I191" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J191" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K191" s="11" t="inlineStr"/>
-      <c r="L191" s="15" t="inlineStr">
+      <c r="J191" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K191" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L191" s="8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -6951,9 +7071,9 @@
       <c r="I192" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J192" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J192" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K192" s="4" t="inlineStr"/>
@@ -6981,9 +7101,9 @@
       <c r="I193" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J193" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J193" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K193" s="11" t="inlineStr"/>
@@ -7041,9 +7161,9 @@
       <c r="I195" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J195" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
+      <c r="J195" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="K195" s="11" t="inlineStr"/>
@@ -7122,7 +7242,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K197" s="11" t="inlineStr"/>
+      <c r="K197" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L197" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -7202,7 +7326,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K199" s="11" t="inlineStr"/>
+      <c r="K199" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L199" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -7282,7 +7410,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K201" s="11" t="inlineStr"/>
+      <c r="K201" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L201" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -7362,7 +7494,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K203" s="11" t="inlineStr"/>
+      <c r="K203" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L203" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -7437,15 +7573,19 @@
       <c r="I205" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J205" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K205" s="11" t="inlineStr"/>
-      <c r="L205" s="15" t="inlineStr">
+      <c r="J205" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K205" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L205" s="9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7692,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K208" s="4" t="inlineStr"/>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L208" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -7657,15 +7801,19 @@
       <c r="I211" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J211" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K211" s="11" t="inlineStr"/>
-      <c r="L211" s="15" t="inlineStr">
+      <c r="J211" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K211" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L211" s="9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -7772,7 +7920,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K214" s="4" t="inlineStr"/>
+      <c r="K214" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L214" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -7817,15 +7969,19 @@
       <c r="I215" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J215" s="15" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K215" s="11" t="inlineStr"/>
-      <c r="L215" s="15" t="inlineStr">
+      <c r="J215" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K215" s="11" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L215" s="8" t="inlineStr">
+        <is>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -7867,15 +8023,19 @@
       <c r="I216" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="J216" s="14" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="K216" s="4" t="inlineStr"/>
-      <c r="L216" s="14" t="inlineStr">
+      <c r="J216" s="8" t="inlineStr">
+        <is>
+          <t>Concluída</t>
+        </is>
+      </c>
+      <c r="K216" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L216" s="9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7952,7 +8112,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K218" s="4" t="inlineStr"/>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L218" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8002,7 +8166,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K219" s="11" t="inlineStr"/>
+      <c r="K219" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L219" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8052,7 +8220,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K220" s="4" t="inlineStr"/>
+      <c r="K220" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L220" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8102,7 +8274,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K221" s="11" t="inlineStr"/>
+      <c r="K221" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L221" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8152,7 +8328,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K222" s="4" t="inlineStr"/>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L222" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8202,7 +8382,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K223" s="11" t="inlineStr"/>
+      <c r="K223" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L223" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8312,7 +8496,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K226" s="4" t="inlineStr"/>
+      <c r="K226" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L226" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8362,7 +8550,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K227" s="11" t="inlineStr"/>
+      <c r="K227" s="11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L227" s="15" t="inlineStr">
         <is>
           <t>0.0%</t>
@@ -8414,7 +8606,11 @@
           <t>Pendente</t>
         </is>
       </c>
-      <c r="K228" s="4" t="inlineStr"/>
+      <c r="K228" s="4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L228" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>

--- a/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
+++ b/projetos/OTZ_ASU_JUNDIAI/push_list/DAENG_PUSH_LIST_ASU_JUNDIAI.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,8 +64,24 @@
       <color rgb="005A7090"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="001A3680"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="007B4F00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001A3680"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +121,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF4FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -181,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -229,6 +250,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L228"/>
+  <dimension ref="A1:L229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1796,7 +1832,7 @@
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -1834,7 +1870,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H37" s="13" t="inlineStr">
@@ -1910,7 +1946,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H39" s="13" t="inlineStr">
@@ -1948,7 +1984,7 @@
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -3172,7 +3208,7 @@
       </c>
       <c r="G76" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
@@ -3526,7 +3562,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H87" s="13" t="inlineStr">
@@ -3760,7 +3796,7 @@
       </c>
       <c r="G94" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
@@ -4114,7 +4150,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H105" s="13" t="inlineStr">
@@ -4348,7 +4384,7 @@
       </c>
       <c r="G112" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
@@ -4582,7 +4618,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H119" s="13" t="inlineStr">
@@ -4936,7 +4972,7 @@
       </c>
       <c r="G130" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
@@ -5170,7 +5206,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H137" s="13" t="inlineStr">
@@ -5404,7 +5440,7 @@
       </c>
       <c r="G144" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
@@ -5638,7 +5674,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H151" s="13" t="inlineStr">
@@ -5992,7 +6028,7 @@
       </c>
       <c r="G162" s="6" t="inlineStr">
         <is>
-          <t>Macrodrenagem / 5S</t>
+          <t>Macrodrenagem</t>
         </is>
       </c>
       <c r="H162" s="7" t="inlineStr">
@@ -8614,6 +8650,66 @@
       <c r="L228" s="14" t="inlineStr">
         <is>
           <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="16" customHeight="1">
+      <c r="A229" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="B229" s="19" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="C229" s="18" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="D229" s="19" t="inlineStr">
+        <is>
+          <t>Entrega de Documentação (Data Book)</t>
+        </is>
+      </c>
+      <c r="E229" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F229" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G229" s="19" t="inlineStr">
+        <is>
+          <t>Contrato</t>
+        </is>
+      </c>
+      <c r="H229" s="20" t="inlineStr">
+        <is>
+          <t>Entrega do Data Book completo da obra</t>
+        </is>
+      </c>
+      <c r="I229" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" s="19" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="K229" s="18" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="L229" s="22" t="inlineStr">
+        <is>
+          <t>Entregável</t>
         </is>
       </c>
     </row>
